--- a/РАБОЧИЙ СТОЛ/расчеты Останкино КИ и ЗПФ/расчеты Останкино ЗПФ/дв 28,09,26 млрсч ост зпф.xlsx
+++ b/РАБОЧИЙ СТОЛ/расчеты Останкино КИ и ЗПФ/расчеты Останкино ЗПФ/дв 28,09,26 млрсч ост зпф.xlsx
@@ -5,16 +5,19 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино ЗПФ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино КИ и ЗПФ\расчеты Останкино ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51F87667-EA17-42A7-9591-C83085EF5790}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CCEBA5E-4884-4375-9143-E8E8F56AAF90}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId2"/>
+  </externalReferences>
   <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -28,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="52">
   <si>
     <t>Номенклатура</t>
   </si>
@@ -76,9 +79,6 @@
   </si>
   <si>
     <t>ср нов</t>
-  </si>
-  <si>
-    <t>расчет</t>
   </si>
   <si>
     <t>кон ост</t>
@@ -175,6 +175,18 @@
   </si>
   <si>
     <t>7216 СОЧНЫЕ СО СЛ.МАСЛ.ПМ пельм пл.0.7кг зам. ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>ТК</t>
+  </si>
+  <si>
+    <t>Титенок</t>
+  </si>
+  <si>
+    <t>заказ</t>
+  </si>
+  <si>
+    <t>05,10,</t>
   </si>
 </sst>
 </file>
@@ -275,7 +287,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -286,6 +298,7 @@
     <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Arial10px" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -302,6 +315,504 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Sheet"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="A3" t="str">
+            <v>Номенклатура</v>
+          </cell>
+          <cell r="B3" t="str">
+            <v>Ед. изм.</v>
+          </cell>
+          <cell r="C3" t="str">
+            <v>Начальный остаток</v>
+          </cell>
+          <cell r="D3" t="str">
+            <v>Приход</v>
+          </cell>
+          <cell r="E3" t="str">
+            <v>Расход</v>
+          </cell>
+          <cell r="F3" t="str">
+            <v>Конечный остаток</v>
+          </cell>
+          <cell r="G3" t="str">
+            <v>крат</v>
+          </cell>
+          <cell r="H3" t="str">
+            <v>сроки</v>
+          </cell>
+          <cell r="I3" t="str">
+            <v>метка</v>
+          </cell>
+          <cell r="J3" t="str">
+            <v>метка2</v>
+          </cell>
+          <cell r="K3" t="str">
+            <v>заяв</v>
+          </cell>
+          <cell r="L3" t="str">
+            <v>разн</v>
+          </cell>
+          <cell r="M3" t="str">
+            <v>без опта</v>
+          </cell>
+          <cell r="N3" t="str">
+            <v>опт</v>
+          </cell>
+          <cell r="O3" t="str">
+            <v>заказ в пути</v>
+          </cell>
+          <cell r="P3" t="str">
+            <v>ср нов</v>
+          </cell>
+          <cell r="Q3" t="str">
+            <v>расчет</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="O4" t="str">
+            <v>28,09,</v>
+          </cell>
+          <cell r="P4" t="str">
+            <v>28,09,</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="E5">
+            <v>74.5</v>
+          </cell>
+          <cell r="F5">
+            <v>1242.32</v>
+          </cell>
+          <cell r="K5">
+            <v>73.5</v>
+          </cell>
+          <cell r="L5">
+            <v>1</v>
+          </cell>
+          <cell r="M5">
+            <v>0</v>
+          </cell>
+          <cell r="N5">
+            <v>0</v>
+          </cell>
+          <cell r="O5">
+            <v>195</v>
+          </cell>
+          <cell r="P5">
+            <v>14.9</v>
+          </cell>
+          <cell r="Q5">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="A6" t="str">
+            <v>5579 БЛИНЧ.КРУГЛЫЕ С САД.ЯБЛОК.пл.1/420 зам. ОСТАНКИНО</v>
+          </cell>
+          <cell r="B6" t="str">
+            <v>шт</v>
+          </cell>
+          <cell r="D6">
+            <v>10</v>
+          </cell>
+          <cell r="F6">
+            <v>10</v>
+          </cell>
+          <cell r="G6">
+            <v>0.42</v>
+          </cell>
+          <cell r="H6">
+            <v>120</v>
+          </cell>
+          <cell r="I6" t="str">
+            <v>матрица</v>
+          </cell>
+          <cell r="L6">
+            <v>0</v>
+          </cell>
+          <cell r="O6">
+            <v>10</v>
+          </cell>
+          <cell r="P6">
+            <v>0</v>
+          </cell>
+          <cell r="R6">
+            <v>50</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7" t="str">
+            <v>5754 БЛИНЧ.КРУГЛЫЕ С МЯСОМ 4,5кг зам. ПМ ОСТАНКИНО</v>
+          </cell>
+          <cell r="B7" t="str">
+            <v>кг</v>
+          </cell>
+          <cell r="C7">
+            <v>184.40799999999999</v>
+          </cell>
+          <cell r="F7">
+            <v>184.40799999999999</v>
+          </cell>
+          <cell r="G7">
+            <v>1</v>
+          </cell>
+          <cell r="H7">
+            <v>120</v>
+          </cell>
+          <cell r="I7" t="str">
+            <v>матрица</v>
+          </cell>
+          <cell r="L7">
+            <v>0</v>
+          </cell>
+          <cell r="P7">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="A8" t="str">
+            <v>5755 БЛИНЧ.КРУГЛЫЕ С ТВОРОГОМ 4,5кг зам. ПМ ОСТАНКИНО</v>
+          </cell>
+          <cell r="B8" t="str">
+            <v>кг</v>
+          </cell>
+          <cell r="C8">
+            <v>62.942</v>
+          </cell>
+          <cell r="E8">
+            <v>4.5</v>
+          </cell>
+          <cell r="F8">
+            <v>53.911999999999999</v>
+          </cell>
+          <cell r="G8">
+            <v>1</v>
+          </cell>
+          <cell r="H8">
+            <v>120</v>
+          </cell>
+          <cell r="I8" t="str">
+            <v>матрица</v>
+          </cell>
+          <cell r="K8">
+            <v>4.5</v>
+          </cell>
+          <cell r="L8">
+            <v>0</v>
+          </cell>
+          <cell r="P8">
+            <v>0.9</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="A9" t="str">
+            <v>5897 БЛИНЧ.КРУГЛЫЕ С ГРУШЕЙ пл.1/420 зам.   ОСТАНКИНО</v>
+          </cell>
+          <cell r="B9" t="str">
+            <v>шт</v>
+          </cell>
+          <cell r="D9">
+            <v>20</v>
+          </cell>
+          <cell r="F9">
+            <v>20</v>
+          </cell>
+          <cell r="G9">
+            <v>0.42</v>
+          </cell>
+          <cell r="H9">
+            <v>120</v>
+          </cell>
+          <cell r="I9" t="str">
+            <v>матрица</v>
+          </cell>
+          <cell r="L9">
+            <v>0</v>
+          </cell>
+          <cell r="P9">
+            <v>0</v>
+          </cell>
+          <cell r="R9">
+            <v>50</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="A10" t="str">
+            <v>6148 БЛИНЧ.КРУГЛЫЕ С ВЕТЧ.И СЫР. ПМ 1/300 зам. ОСТАНКИНО</v>
+          </cell>
+          <cell r="B10" t="str">
+            <v>шт</v>
+          </cell>
+          <cell r="C10">
+            <v>217</v>
+          </cell>
+          <cell r="E10">
+            <v>7</v>
+          </cell>
+          <cell r="F10">
+            <v>209</v>
+          </cell>
+          <cell r="G10">
+            <v>0.3</v>
+          </cell>
+          <cell r="H10">
+            <v>120</v>
+          </cell>
+          <cell r="I10" t="str">
+            <v>матрица</v>
+          </cell>
+          <cell r="K10">
+            <v>7</v>
+          </cell>
+          <cell r="L10">
+            <v>0</v>
+          </cell>
+          <cell r="P10">
+            <v>1.4</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="A11" t="str">
+            <v>6149 БЛИНЧ.КРУГЛЫЕ С ПЕЧЕНЬЮ ПМ 1/300 зам. ОСТАНКИНО</v>
+          </cell>
+          <cell r="B11" t="str">
+            <v>шт</v>
+          </cell>
+          <cell r="C11">
+            <v>49</v>
+          </cell>
+          <cell r="E11">
+            <v>6</v>
+          </cell>
+          <cell r="F11">
+            <v>42</v>
+          </cell>
+          <cell r="G11">
+            <v>0.3</v>
+          </cell>
+          <cell r="H11">
+            <v>120</v>
+          </cell>
+          <cell r="I11" t="str">
+            <v>матрица</v>
+          </cell>
+          <cell r="K11">
+            <v>6</v>
+          </cell>
+          <cell r="L11">
+            <v>0</v>
+          </cell>
+          <cell r="O11">
+            <v>100</v>
+          </cell>
+          <cell r="P11">
+            <v>1.2</v>
+          </cell>
+          <cell r="R11">
+            <v>150</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="A12" t="str">
+            <v>6168 Блинчики с мясом пл. 1/350 зам. ОСТАНКИНО</v>
+          </cell>
+          <cell r="B12" t="str">
+            <v>шт</v>
+          </cell>
+          <cell r="C12">
+            <v>269</v>
+          </cell>
+          <cell r="E12">
+            <v>15</v>
+          </cell>
+          <cell r="F12">
+            <v>250</v>
+          </cell>
+          <cell r="G12">
+            <v>0.35</v>
+          </cell>
+          <cell r="H12">
+            <v>120</v>
+          </cell>
+          <cell r="I12" t="str">
+            <v>матрица</v>
+          </cell>
+          <cell r="K12">
+            <v>15</v>
+          </cell>
+          <cell r="L12">
+            <v>0</v>
+          </cell>
+          <cell r="P12">
+            <v>3</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="A13" t="str">
+            <v>6202 БЛИНЧ.КРУГЛЫЕ С ТВОРОГОМ ПМ 1/300 зам. ОСТАНКИНО</v>
+          </cell>
+          <cell r="B13" t="str">
+            <v>шт</v>
+          </cell>
+          <cell r="C13">
+            <v>20</v>
+          </cell>
+          <cell r="D13">
+            <v>24</v>
+          </cell>
+          <cell r="E13">
+            <v>5</v>
+          </cell>
+          <cell r="F13">
+            <v>38</v>
+          </cell>
+          <cell r="G13">
+            <v>0.3</v>
+          </cell>
+          <cell r="H13">
+            <v>120</v>
+          </cell>
+          <cell r="I13" t="str">
+            <v>матрица</v>
+          </cell>
+          <cell r="K13">
+            <v>4</v>
+          </cell>
+          <cell r="L13">
+            <v>1</v>
+          </cell>
+          <cell r="O13">
+            <v>40</v>
+          </cell>
+          <cell r="P13">
+            <v>1</v>
+          </cell>
+          <cell r="R13">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="A14" t="str">
+            <v>6209 Блинчики с куриным мясом пл. 1/350 зам. ОСТАНКИНО</v>
+          </cell>
+          <cell r="B14" t="str">
+            <v>шт</v>
+          </cell>
+          <cell r="C14">
+            <v>243</v>
+          </cell>
+          <cell r="E14">
+            <v>12</v>
+          </cell>
+          <cell r="F14">
+            <v>227</v>
+          </cell>
+          <cell r="G14">
+            <v>0.35</v>
+          </cell>
+          <cell r="H14">
+            <v>120</v>
+          </cell>
+          <cell r="I14" t="str">
+            <v>матрица</v>
+          </cell>
+          <cell r="K14">
+            <v>12</v>
+          </cell>
+          <cell r="L14">
+            <v>0</v>
+          </cell>
+          <cell r="O14">
+            <v>45</v>
+          </cell>
+          <cell r="P14">
+            <v>2.4</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="A15" t="str">
+            <v>6819 БЛИНЧ.КРУГЛЫЕ С САД.ЯБЛОК. пл. 1/300 зам. ОСТАНКИНО</v>
+          </cell>
+          <cell r="B15" t="str">
+            <v>шт</v>
+          </cell>
+          <cell r="C15">
+            <v>101</v>
+          </cell>
+          <cell r="F15">
+            <v>101</v>
+          </cell>
+          <cell r="G15">
+            <v>0.3</v>
+          </cell>
+          <cell r="H15">
+            <v>120</v>
+          </cell>
+          <cell r="I15" t="str">
+            <v>матрица</v>
+          </cell>
+          <cell r="L15">
+            <v>0</v>
+          </cell>
+          <cell r="P15">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="A16" t="str">
+            <v>7216 СОЧНЫЕ СО СЛ.МАСЛ.ПМ пельм пл.0.7кг зам. ОСТАНКИНО</v>
+          </cell>
+          <cell r="B16" t="str">
+            <v>шт</v>
+          </cell>
+          <cell r="C16">
+            <v>102</v>
+          </cell>
+          <cell r="D16">
+            <v>30</v>
+          </cell>
+          <cell r="E16">
+            <v>25</v>
+          </cell>
+          <cell r="F16">
+            <v>107</v>
+          </cell>
+          <cell r="G16">
+            <v>0.7</v>
+          </cell>
+          <cell r="H16">
+            <v>180</v>
+          </cell>
+          <cell r="I16" t="str">
+            <v>матрица</v>
+          </cell>
+          <cell r="K16">
+            <v>25</v>
+          </cell>
+          <cell r="L16">
+            <v>0</v>
+          </cell>
+          <cell r="P16">
+            <v>5</v>
+          </cell>
+          <cell r="R16">
+            <v>150</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -589,7 +1100,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AV500"/>
+  <dimension ref="A1:AW500"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
@@ -602,15 +1113,15 @@
     <col min="10" max="10" width="1" customWidth="1"/>
     <col min="11" max="12" width="7" customWidth="1"/>
     <col min="13" max="14" width="0.28515625" customWidth="1"/>
-    <col min="15" max="17" width="7" customWidth="1"/>
-    <col min="18" max="19" width="5" customWidth="1"/>
-    <col min="20" max="29" width="6" customWidth="1"/>
-    <col min="30" max="30" width="47.7109375" customWidth="1"/>
-    <col min="31" max="31" width="7" customWidth="1"/>
-    <col min="32" max="48" width="8" customWidth="1"/>
+    <col min="15" max="18" width="7" customWidth="1"/>
+    <col min="19" max="20" width="5" customWidth="1"/>
+    <col min="21" max="30" width="6" customWidth="1"/>
+    <col min="31" max="31" width="47.7109375" customWidth="1"/>
+    <col min="32" max="32" width="7" customWidth="1"/>
+    <col min="33" max="49" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -659,8 +1170,9 @@
       <c r="AT1" s="1"/>
       <c r="AU1" s="1"/>
       <c r="AV1" s="1"/>
-    </row>
-    <row r="2" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW1" s="1"/>
+    </row>
+    <row r="2" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -709,8 +1221,9 @@
       <c r="AT2" s="1"/>
       <c r="AU2" s="1"/>
       <c r="AV2" s="1"/>
-    </row>
-    <row r="3" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW2" s="1"/>
+    </row>
+    <row r="3" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -760,51 +1273,53 @@
         <v>15</v>
       </c>
       <c r="Q3" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="S3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="2" t="s">
+      <c r="T3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S3" s="2" t="s">
+      <c r="U3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T3" s="2" t="s">
+      <c r="V3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="X3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AB3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AD3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AE3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="V3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="W3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="X3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="Y3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="Z3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AA3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AB3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AC3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD3" s="2" t="s">
+      <c r="AF3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="AE3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="AF3" s="1"/>
       <c r="AG3" s="1"/>
       <c r="AH3" s="1"/>
       <c r="AI3" s="1"/>
@@ -821,8 +1336,9 @@
       <c r="AT3" s="1"/>
       <c r="AU3" s="1"/>
       <c r="AV3" s="1"/>
-    </row>
-    <row r="4" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW3" s="1"/>
+    </row>
+    <row r="4" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -838,45 +1354,49 @@
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S4" s="1"/>
+      <c r="T4" s="1"/>
+      <c r="U4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="V4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="P4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q4" s="1"/>
-      <c r="R4" s="1"/>
-      <c r="S4" s="1"/>
-      <c r="T4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="U4" s="1" t="s">
+      <c r="W4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="V4" s="1" t="s">
+      <c r="X4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="W4" s="1" t="s">
+      <c r="Y4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="X4" s="1" t="s">
+      <c r="Z4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="Y4" s="1" t="s">
+      <c r="AA4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="Z4" s="1" t="s">
+      <c r="AB4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AA4" s="1" t="s">
+      <c r="AC4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AB4" s="1" t="s">
+      <c r="AD4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AC4" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="AD4" s="1"/>
       <c r="AE4" s="1"/>
       <c r="AF4" s="1"/>
       <c r="AG4" s="1"/>
@@ -895,8 +1415,9 @@
       <c r="AT4" s="1"/>
       <c r="AU4" s="1"/>
       <c r="AV4" s="1"/>
-    </row>
-    <row r="5" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW4" s="1"/>
+    </row>
+    <row r="5" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -939,56 +1460,56 @@
       </c>
       <c r="Q5" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R5" s="1"/>
+        <v>170</v>
+      </c>
+      <c r="R5" s="4"/>
       <c r="S5" s="1"/>
-      <c r="T5" s="4">
-        <f t="shared" ref="T5:AC5" si="1">SUM(T6:T500)</f>
+      <c r="T5" s="1"/>
+      <c r="U5" s="4">
+        <f t="shared" ref="U5:AD5" si="1">SUM(U6:U500)</f>
         <v>67.129599999999996</v>
       </c>
-      <c r="U5" s="4">
+      <c r="V5" s="4">
         <f t="shared" si="1"/>
         <v>51.828400000000002</v>
       </c>
-      <c r="V5" s="4">
+      <c r="W5" s="4">
         <f t="shared" si="1"/>
         <v>21.6</v>
       </c>
-      <c r="W5" s="4">
+      <c r="X5" s="4">
         <f t="shared" si="1"/>
         <v>100.2</v>
       </c>
-      <c r="X5" s="4">
+      <c r="Y5" s="4">
         <f t="shared" si="1"/>
         <v>57.6</v>
       </c>
-      <c r="Y5" s="4">
+      <c r="Z5" s="4">
         <f t="shared" si="1"/>
         <v>15.600000000000001</v>
       </c>
-      <c r="Z5" s="4">
+      <c r="AA5" s="4">
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
-      <c r="AA5" s="4">
+      <c r="AB5" s="4">
         <f t="shared" si="1"/>
         <v>136.226</v>
       </c>
-      <c r="AB5" s="4">
+      <c r="AC5" s="4">
         <f t="shared" si="1"/>
         <v>45.400000000000006</v>
       </c>
-      <c r="AC5" s="4">
+      <c r="AD5" s="4">
         <f t="shared" si="1"/>
         <v>81.2</v>
       </c>
-      <c r="AD5" s="1"/>
-      <c r="AE5" s="4">
-        <f>SUM(AE6:AE500)</f>
-        <v>0</v>
-      </c>
-      <c r="AF5" s="1"/>
+      <c r="AE5" s="1"/>
+      <c r="AF5" s="4">
+        <f>SUM(AF6:AF500)</f>
+        <v>80.599999999999994</v>
+      </c>
       <c r="AG5" s="1"/>
       <c r="AH5" s="1"/>
       <c r="AI5" s="1"/>
@@ -1005,13 +1526,14 @@
       <c r="AT5" s="1"/>
       <c r="AU5" s="1"/>
       <c r="AV5" s="1"/>
-    </row>
-    <row r="6" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW5" s="1"/>
+    </row>
+    <row r="6" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>34</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1">
@@ -1028,7 +1550,7 @@
         <v>120</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
@@ -1045,53 +1567,58 @@
         <f>E6/5</f>
         <v>0</v>
       </c>
-      <c r="Q6" s="5"/>
-      <c r="R6" s="1" t="e">
+      <c r="Q6" s="5">
+        <v>40</v>
+      </c>
+      <c r="R6" s="10">
+        <f>VLOOKUP(A6,[1]Sheet!$A:$R,18,0)</f>
+        <v>50</v>
+      </c>
+      <c r="S6" s="1" t="e">
         <f>(F6+O6+Q6)/P6</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S6" s="1" t="e">
+      <c r="T6" s="1" t="e">
         <f>(F6+O6)/P6</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="T6" s="1">
+      <c r="U6" s="1">
         <v>0</v>
       </c>
-      <c r="U6" s="1">
+      <c r="V6" s="1">
         <v>1</v>
       </c>
-      <c r="V6" s="1">
+      <c r="W6" s="1">
         <v>0</v>
       </c>
-      <c r="W6" s="1">
+      <c r="X6" s="1">
         <v>2.2000000000000002</v>
-      </c>
-      <c r="X6" s="1">
-        <v>0.6</v>
       </c>
       <c r="Y6" s="1">
         <v>0.6</v>
       </c>
       <c r="Z6" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="AA6" s="1">
         <v>0</v>
       </c>
-      <c r="AA6" s="1">
+      <c r="AB6" s="1">
         <v>8.4</v>
       </c>
-      <c r="AB6" s="1">
+      <c r="AC6" s="1">
         <v>1</v>
       </c>
-      <c r="AC6" s="1">
+      <c r="AD6" s="1">
         <v>9</v>
       </c>
-      <c r="AD6" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AE6" s="1">
-        <f>G6*Q6</f>
-        <v>0</v>
-      </c>
-      <c r="AF6" s="1"/>
+      <c r="AE6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AF6" s="1">
+        <f t="shared" ref="AF6:AF16" si="3">G6*Q6</f>
+        <v>16.8</v>
+      </c>
       <c r="AG6" s="1"/>
       <c r="AH6" s="1"/>
       <c r="AI6" s="1"/>
@@ -1108,13 +1635,14 @@
       <c r="AT6" s="1"/>
       <c r="AU6" s="1"/>
       <c r="AV6" s="1"/>
-    </row>
-    <row r="7" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW6" s="1"/>
+    </row>
+    <row r="7" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>38</v>
       </c>
       <c r="C7" s="1">
         <v>184.40799999999999</v>
@@ -1131,7 +1659,7 @@
         <v>120</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
@@ -1143,26 +1671,24 @@
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
       <c r="P7" s="1">
-        <f t="shared" ref="P7:P16" si="3">E7/5</f>
+        <f t="shared" ref="P7:P16" si="4">E7/5</f>
         <v>0</v>
       </c>
       <c r="Q7" s="5"/>
-      <c r="R7" s="1" t="e">
-        <f t="shared" ref="R7:R16" si="4">(F7+O7+Q7)/P7</f>
+      <c r="R7" s="10"/>
+      <c r="S7" s="1" t="e">
+        <f t="shared" ref="S7:S16" si="5">(F7+O7+Q7)/P7</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S7" s="1" t="e">
-        <f t="shared" ref="S7:S16" si="5">(F7+O7)/P7</f>
+      <c r="T7" s="1" t="e">
+        <f t="shared" ref="T7:T16" si="6">(F7+O7)/P7</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="T7" s="1">
+      <c r="U7" s="1">
         <v>0.91799999999999993</v>
       </c>
-      <c r="U7" s="1">
+      <c r="V7" s="1">
         <v>0.91679999999999995</v>
-      </c>
-      <c r="V7" s="1">
-        <v>0</v>
       </c>
       <c r="W7" s="1">
         <v>0</v>
@@ -1177,22 +1703,24 @@
         <v>0</v>
       </c>
       <c r="AA7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="1">
         <v>0.91880000000000006</v>
-      </c>
-      <c r="AB7" s="1">
-        <v>0</v>
       </c>
       <c r="AC7" s="1">
         <v>0</v>
       </c>
-      <c r="AD7" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="AE7" s="1">
-        <f>G7*Q7</f>
+      <c r="AD7" s="1">
         <v>0</v>
       </c>
-      <c r="AF7" s="1"/>
+      <c r="AE7" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="AF7" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="AG7" s="1"/>
       <c r="AH7" s="1"/>
       <c r="AI7" s="1"/>
@@ -1209,13 +1737,14 @@
       <c r="AT7" s="1"/>
       <c r="AU7" s="1"/>
       <c r="AV7" s="1"/>
-    </row>
-    <row r="8" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW7" s="1"/>
+    </row>
+    <row r="8" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C8" s="1">
         <v>62.942</v>
@@ -1234,7 +1763,7 @@
         <v>120</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J8" s="1"/>
       <c r="K8" s="1">
@@ -1248,26 +1777,24 @@
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
       <c r="P8" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.9</v>
       </c>
       <c r="Q8" s="5"/>
-      <c r="R8" s="1">
-        <f t="shared" si="4"/>
-        <v>59.902222222222221</v>
-      </c>
+      <c r="R8" s="10"/>
       <c r="S8" s="1">
         <f t="shared" si="5"/>
         <v>59.902222222222221</v>
       </c>
       <c r="T8" s="1">
+        <f t="shared" si="6"/>
+        <v>59.902222222222221</v>
+      </c>
+      <c r="U8" s="1">
         <v>1.8116000000000001</v>
       </c>
-      <c r="U8" s="1">
+      <c r="V8" s="1">
         <v>0.91159999999999997</v>
-      </c>
-      <c r="V8" s="1">
-        <v>0</v>
       </c>
       <c r="W8" s="1">
         <v>0</v>
@@ -1282,22 +1809,24 @@
         <v>0</v>
       </c>
       <c r="AA8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="1">
         <v>0.9071999999999999</v>
-      </c>
-      <c r="AB8" s="1">
-        <v>0</v>
       </c>
       <c r="AC8" s="1">
         <v>0</v>
       </c>
-      <c r="AD8" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="AE8" s="1">
-        <f>G8*Q8</f>
+      <c r="AD8" s="1">
         <v>0</v>
       </c>
-      <c r="AF8" s="1"/>
+      <c r="AE8" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="AF8" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="AG8" s="1"/>
       <c r="AH8" s="1"/>
       <c r="AI8" s="1"/>
@@ -1314,13 +1843,14 @@
       <c r="AT8" s="1"/>
       <c r="AU8" s="1"/>
       <c r="AV8" s="1"/>
-    </row>
-    <row r="9" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW8" s="1"/>
+    </row>
+    <row r="9" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1">
@@ -1337,7 +1867,7 @@
         <v>120</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
@@ -1349,20 +1879,23 @@
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
       <c r="P9" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="Q9" s="5"/>
-      <c r="R9" s="1" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+      <c r="Q9" s="5">
+        <v>40</v>
+      </c>
+      <c r="R9" s="10">
+        <f>VLOOKUP(A9,[1]Sheet!$A:$R,18,0)</f>
+        <v>50</v>
       </c>
       <c r="S9" s="1" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T9" s="1">
-        <v>0</v>
+      <c r="T9" s="1" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
       </c>
       <c r="U9" s="1">
         <v>0</v>
@@ -1391,12 +1924,14 @@
       <c r="AC9" s="1">
         <v>0</v>
       </c>
-      <c r="AD9" s="1"/>
-      <c r="AE9" s="1">
-        <f>G9*Q9</f>
+      <c r="AD9" s="1">
         <v>0</v>
       </c>
-      <c r="AF9" s="1"/>
+      <c r="AE9" s="1"/>
+      <c r="AF9" s="1">
+        <f t="shared" si="3"/>
+        <v>16.8</v>
+      </c>
       <c r="AG9" s="1"/>
       <c r="AH9" s="1"/>
       <c r="AI9" s="1"/>
@@ -1413,13 +1948,14 @@
       <c r="AT9" s="1"/>
       <c r="AU9" s="1"/>
       <c r="AV9" s="1"/>
-    </row>
-    <row r="10" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW9" s="1"/>
+    </row>
+    <row r="10" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" s="1">
         <v>217</v>
@@ -1438,7 +1974,7 @@
         <v>120</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J10" s="1"/>
       <c r="K10" s="1">
@@ -1452,56 +1988,56 @@
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
       <c r="P10" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.4</v>
       </c>
       <c r="Q10" s="5"/>
-      <c r="R10" s="1">
-        <f t="shared" si="4"/>
-        <v>149.28571428571431</v>
-      </c>
+      <c r="R10" s="10"/>
       <c r="S10" s="1">
         <f t="shared" si="5"/>
         <v>149.28571428571431</v>
       </c>
       <c r="T10" s="1">
+        <f t="shared" si="6"/>
+        <v>149.28571428571431</v>
+      </c>
+      <c r="U10" s="1">
         <v>13</v>
       </c>
-      <c r="U10" s="1">
+      <c r="V10" s="1">
         <v>5.8</v>
       </c>
-      <c r="V10" s="1">
+      <c r="W10" s="1">
         <v>3.4</v>
       </c>
-      <c r="W10" s="1">
+      <c r="X10" s="1">
         <v>21.6</v>
       </c>
-      <c r="X10" s="1">
+      <c r="Y10" s="1">
         <v>12.2</v>
       </c>
-      <c r="Y10" s="1">
+      <c r="Z10" s="1">
         <v>1.2</v>
       </c>
-      <c r="Z10" s="1">
+      <c r="AA10" s="1">
         <v>2.4</v>
       </c>
-      <c r="AA10" s="1">
+      <c r="AB10" s="1">
         <v>37.4</v>
       </c>
-      <c r="AB10" s="1">
+      <c r="AC10" s="1">
         <v>16</v>
       </c>
-      <c r="AC10" s="1">
+      <c r="AD10" s="1">
         <v>18.2</v>
       </c>
-      <c r="AD10" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="AE10" s="1">
-        <f>G10*Q10</f>
+      <c r="AE10" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="AF10" s="1">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AF10" s="1"/>
       <c r="AG10" s="1"/>
       <c r="AH10" s="1"/>
       <c r="AI10" s="1"/>
@@ -1518,13 +2054,14 @@
       <c r="AT10" s="1"/>
       <c r="AU10" s="1"/>
       <c r="AV10" s="1"/>
-    </row>
-    <row r="11" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW10" s="1"/>
+    </row>
+    <row r="11" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C11" s="1">
         <v>49</v>
@@ -1543,7 +2080,7 @@
         <v>120</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J11" s="1"/>
       <c r="K11" s="1">
@@ -1559,56 +2096,61 @@
         <v>100</v>
       </c>
       <c r="P11" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.2</v>
       </c>
-      <c r="Q11" s="5"/>
-      <c r="R11" s="1">
-        <f t="shared" si="4"/>
-        <v>118.33333333333334</v>
+      <c r="Q11" s="5">
+        <v>20</v>
+      </c>
+      <c r="R11" s="10">
+        <f>VLOOKUP(A11,[1]Sheet!$A:$R,18,0)</f>
+        <v>150</v>
       </c>
       <c r="S11" s="1">
         <f t="shared" si="5"/>
+        <v>135</v>
+      </c>
+      <c r="T11" s="1">
+        <f t="shared" si="6"/>
         <v>118.33333333333334</v>
       </c>
-      <c r="T11" s="1">
+      <c r="U11" s="1">
         <v>9.6</v>
       </c>
-      <c r="U11" s="1">
+      <c r="V11" s="1">
         <v>3.4</v>
       </c>
-      <c r="V11" s="1">
+      <c r="W11" s="1">
         <v>3.6</v>
       </c>
-      <c r="W11" s="1">
+      <c r="X11" s="1">
         <v>9</v>
       </c>
-      <c r="X11" s="1">
+      <c r="Y11" s="1">
         <v>5.8</v>
       </c>
-      <c r="Y11" s="1">
+      <c r="Z11" s="1">
         <v>1.4</v>
       </c>
-      <c r="Z11" s="1">
+      <c r="AA11" s="1">
         <v>4.4000000000000004</v>
       </c>
-      <c r="AA11" s="1">
+      <c r="AB11" s="1">
         <v>8.8000000000000007</v>
       </c>
-      <c r="AB11" s="1">
+      <c r="AC11" s="1">
         <v>4.4000000000000004</v>
       </c>
-      <c r="AC11" s="1">
+      <c r="AD11" s="1">
         <v>15.4</v>
       </c>
-      <c r="AD11" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="AE11" s="1">
-        <f>G11*Q11</f>
-        <v>0</v>
-      </c>
-      <c r="AF11" s="1"/>
+      <c r="AE11" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="AF11" s="1">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
       <c r="AG11" s="1"/>
       <c r="AH11" s="1"/>
       <c r="AI11" s="1"/>
@@ -1625,13 +2167,14 @@
       <c r="AT11" s="1"/>
       <c r="AU11" s="1"/>
       <c r="AV11" s="1"/>
-    </row>
-    <row r="12" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW11" s="1"/>
+    </row>
+    <row r="12" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" s="1">
         <v>269</v>
@@ -1650,7 +2193,7 @@
         <v>120</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J12" s="1"/>
       <c r="K12" s="1">
@@ -1664,56 +2207,56 @@
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
       <c r="P12" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="Q12" s="5"/>
-      <c r="R12" s="1">
-        <f t="shared" si="4"/>
-        <v>83.333333333333329</v>
-      </c>
+      <c r="R12" s="10"/>
       <c r="S12" s="1">
         <f t="shared" si="5"/>
         <v>83.333333333333329</v>
       </c>
       <c r="T12" s="1">
+        <f t="shared" si="6"/>
+        <v>83.333333333333329</v>
+      </c>
+      <c r="U12" s="1">
         <v>8.1999999999999993</v>
       </c>
-      <c r="U12" s="1">
+      <c r="V12" s="1">
         <v>11</v>
       </c>
-      <c r="V12" s="1">
+      <c r="W12" s="1">
         <v>2.6</v>
       </c>
-      <c r="W12" s="1">
+      <c r="X12" s="1">
         <v>24.6</v>
       </c>
-      <c r="X12" s="1">
+      <c r="Y12" s="1">
         <v>11.8</v>
       </c>
-      <c r="Y12" s="1">
+      <c r="Z12" s="1">
         <v>2.4</v>
       </c>
-      <c r="Z12" s="1">
+      <c r="AA12" s="1">
         <v>2.6</v>
       </c>
-      <c r="AA12" s="1">
+      <c r="AB12" s="1">
         <v>37.6</v>
       </c>
-      <c r="AB12" s="1">
+      <c r="AC12" s="1">
         <v>0.6</v>
       </c>
-      <c r="AC12" s="1">
+      <c r="AD12" s="1">
         <v>-0.6</v>
       </c>
-      <c r="AD12" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="AE12" s="1">
-        <f>G12*Q12</f>
+      <c r="AE12" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="AF12" s="1">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AF12" s="1"/>
       <c r="AG12" s="1"/>
       <c r="AH12" s="1"/>
       <c r="AI12" s="1"/>
@@ -1730,13 +2273,14 @@
       <c r="AT12" s="1"/>
       <c r="AU12" s="1"/>
       <c r="AV12" s="1"/>
-    </row>
-    <row r="13" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW12" s="1"/>
+    </row>
+    <row r="13" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C13" s="1">
         <v>20</v>
@@ -1757,7 +2301,7 @@
         <v>120</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J13" s="1"/>
       <c r="K13" s="1">
@@ -1773,56 +2317,61 @@
         <v>40</v>
       </c>
       <c r="P13" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="Q13" s="5"/>
-      <c r="R13" s="1">
-        <f t="shared" si="4"/>
-        <v>78</v>
+      <c r="Q13" s="5">
+        <v>20</v>
+      </c>
+      <c r="R13" s="10">
+        <f>VLOOKUP(A13,[1]Sheet!$A:$R,18,0)</f>
+        <v>100</v>
       </c>
       <c r="S13" s="1">
         <f t="shared" si="5"/>
+        <v>98</v>
+      </c>
+      <c r="T13" s="1">
+        <f t="shared" si="6"/>
         <v>78</v>
       </c>
-      <c r="T13" s="1">
+      <c r="U13" s="1">
         <v>6</v>
       </c>
-      <c r="U13" s="1">
+      <c r="V13" s="1">
         <v>4.8</v>
       </c>
-      <c r="V13" s="1">
+      <c r="W13" s="1">
         <v>3</v>
       </c>
-      <c r="W13" s="1">
+      <c r="X13" s="1">
         <v>6.8</v>
       </c>
-      <c r="X13" s="1">
+      <c r="Y13" s="1">
         <v>5.8</v>
       </c>
-      <c r="Y13" s="1">
+      <c r="Z13" s="1">
         <v>3.2</v>
       </c>
-      <c r="Z13" s="1">
+      <c r="AA13" s="1">
         <v>3.8</v>
       </c>
-      <c r="AA13" s="1">
+      <c r="AB13" s="1">
         <v>0.2</v>
       </c>
-      <c r="AB13" s="1">
+      <c r="AC13" s="1">
         <v>5</v>
       </c>
-      <c r="AC13" s="1">
+      <c r="AD13" s="1">
         <v>10.6</v>
       </c>
-      <c r="AD13" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="AE13" s="1">
-        <f>G13*Q13</f>
-        <v>0</v>
-      </c>
-      <c r="AF13" s="1"/>
+      <c r="AE13" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="AF13" s="1">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
       <c r="AG13" s="1"/>
       <c r="AH13" s="1"/>
       <c r="AI13" s="1"/>
@@ -1839,13 +2388,14 @@
       <c r="AT13" s="1"/>
       <c r="AU13" s="1"/>
       <c r="AV13" s="1"/>
-    </row>
-    <row r="14" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW13" s="1"/>
+    </row>
+    <row r="14" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C14" s="1">
         <v>243</v>
@@ -1864,7 +2414,7 @@
         <v>120</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J14" s="1"/>
       <c r="K14" s="1">
@@ -1880,56 +2430,56 @@
         <v>45</v>
       </c>
       <c r="P14" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.4</v>
       </c>
       <c r="Q14" s="5"/>
-      <c r="R14" s="1">
-        <f t="shared" si="4"/>
-        <v>113.33333333333334</v>
-      </c>
+      <c r="R14" s="10"/>
       <c r="S14" s="1">
         <f t="shared" si="5"/>
         <v>113.33333333333334</v>
       </c>
       <c r="T14" s="1">
+        <f t="shared" si="6"/>
+        <v>113.33333333333334</v>
+      </c>
+      <c r="U14" s="1">
         <v>18.8</v>
       </c>
-      <c r="U14" s="1">
+      <c r="V14" s="1">
         <v>13.4</v>
       </c>
-      <c r="V14" s="1">
+      <c r="W14" s="1">
         <v>5</v>
       </c>
-      <c r="W14" s="1">
+      <c r="X14" s="1">
         <v>29.2</v>
       </c>
-      <c r="X14" s="1">
+      <c r="Y14" s="1">
         <v>19.600000000000001</v>
       </c>
-      <c r="Y14" s="1">
+      <c r="Z14" s="1">
         <v>3.8</v>
       </c>
-      <c r="Z14" s="1">
+      <c r="AA14" s="1">
         <v>4.4000000000000004</v>
       </c>
-      <c r="AA14" s="1">
+      <c r="AB14" s="1">
         <v>39.4</v>
       </c>
-      <c r="AB14" s="1">
+      <c r="AC14" s="1">
         <v>16.2</v>
       </c>
-      <c r="AC14" s="1">
+      <c r="AD14" s="1">
         <v>22.8</v>
       </c>
-      <c r="AD14" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="AE14" s="1">
-        <f>G14*Q14</f>
+      <c r="AE14" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="AF14" s="1">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AF14" s="1"/>
       <c r="AG14" s="1"/>
       <c r="AH14" s="1"/>
       <c r="AI14" s="1"/>
@@ -1946,13 +2496,14 @@
       <c r="AT14" s="1"/>
       <c r="AU14" s="1"/>
       <c r="AV14" s="1"/>
-    </row>
-    <row r="15" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW14" s="1"/>
+    </row>
+    <row r="15" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C15" s="1">
         <v>101</v>
@@ -1969,7 +2520,7 @@
         <v>120</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
@@ -1981,56 +2532,56 @@
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
       <c r="P15" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q15" s="5"/>
-      <c r="R15" s="1" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="R15" s="10"/>
       <c r="S15" s="1" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T15" s="1">
-        <v>0.2</v>
+      <c r="T15" s="1" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
       </c>
       <c r="U15" s="1">
         <v>0.2</v>
       </c>
       <c r="V15" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="W15" s="1">
         <v>0</v>
       </c>
-      <c r="W15" s="1">
+      <c r="X15" s="1">
         <v>1</v>
-      </c>
-      <c r="X15" s="1">
-        <v>0.6</v>
       </c>
       <c r="Y15" s="1">
         <v>0.6</v>
       </c>
       <c r="Z15" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="AA15" s="1">
         <v>0.4</v>
       </c>
-      <c r="AA15" s="1">
+      <c r="AB15" s="1">
         <v>1</v>
-      </c>
-      <c r="AB15" s="1">
-        <v>0</v>
       </c>
       <c r="AC15" s="1">
         <v>0</v>
       </c>
-      <c r="AD15" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="AE15" s="1">
-        <f>G15*Q15</f>
+      <c r="AD15" s="1">
         <v>0</v>
       </c>
-      <c r="AF15" s="1"/>
+      <c r="AE15" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="AF15" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="AG15" s="1"/>
       <c r="AH15" s="1"/>
       <c r="AI15" s="1"/>
@@ -2047,13 +2598,14 @@
       <c r="AT15" s="1"/>
       <c r="AU15" s="1"/>
       <c r="AV15" s="1"/>
-    </row>
-    <row r="16" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW15" s="1"/>
+    </row>
+    <row r="16" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C16" s="1">
         <v>102</v>
@@ -2074,7 +2626,7 @@
         <v>180</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J16" s="1"/>
       <c r="K16" s="1">
@@ -2088,54 +2640,59 @@
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
       <c r="P16" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="Q16" s="5"/>
-      <c r="R16" s="1">
-        <f t="shared" si="4"/>
-        <v>21.4</v>
+      <c r="Q16" s="5">
+        <v>50</v>
+      </c>
+      <c r="R16" s="10">
+        <f>VLOOKUP(A16,[1]Sheet!$A:$R,18,0)</f>
+        <v>150</v>
       </c>
       <c r="S16" s="1">
         <f t="shared" si="5"/>
+        <v>31.4</v>
+      </c>
+      <c r="T16" s="1">
+        <f t="shared" si="6"/>
         <v>21.4</v>
       </c>
-      <c r="T16" s="1">
+      <c r="U16" s="1">
         <v>8.6</v>
       </c>
-      <c r="U16" s="1">
+      <c r="V16" s="1">
         <v>10.4</v>
       </c>
-      <c r="V16" s="1">
+      <c r="W16" s="1">
         <v>4</v>
       </c>
-      <c r="W16" s="1">
+      <c r="X16" s="1">
         <v>5.8</v>
       </c>
-      <c r="X16" s="1">
+      <c r="Y16" s="1">
         <v>1.2</v>
       </c>
-      <c r="Y16" s="1">
+      <c r="Z16" s="1">
         <v>2.4</v>
       </c>
-      <c r="Z16" s="1">
+      <c r="AA16" s="1">
         <v>1</v>
       </c>
-      <c r="AA16" s="1">
+      <c r="AB16" s="1">
         <v>1.6</v>
       </c>
-      <c r="AB16" s="1">
+      <c r="AC16" s="1">
         <v>2.2000000000000002</v>
       </c>
-      <c r="AC16" s="1">
+      <c r="AD16" s="1">
         <v>5.8</v>
       </c>
-      <c r="AD16" s="1"/>
-      <c r="AE16" s="1">
-        <f>G16*Q16</f>
-        <v>0</v>
-      </c>
-      <c r="AF16" s="1"/>
+      <c r="AE16" s="1"/>
+      <c r="AF16" s="1">
+        <f t="shared" si="3"/>
+        <v>35</v>
+      </c>
       <c r="AG16" s="1"/>
       <c r="AH16" s="1"/>
       <c r="AI16" s="1"/>
@@ -2152,8 +2709,9 @@
       <c r="AT16" s="1"/>
       <c r="AU16" s="1"/>
       <c r="AV16" s="1"/>
-    </row>
-    <row r="17" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW16" s="1"/>
+    </row>
+    <row r="17" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -2202,8 +2760,9 @@
       <c r="AT17" s="1"/>
       <c r="AU17" s="1"/>
       <c r="AV17" s="1"/>
-    </row>
-    <row r="18" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW17" s="1"/>
+    </row>
+    <row r="18" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -2252,8 +2811,9 @@
       <c r="AT18" s="1"/>
       <c r="AU18" s="1"/>
       <c r="AV18" s="1"/>
-    </row>
-    <row r="19" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW18" s="1"/>
+    </row>
+    <row r="19" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -2302,8 +2862,9 @@
       <c r="AT19" s="1"/>
       <c r="AU19" s="1"/>
       <c r="AV19" s="1"/>
-    </row>
-    <row r="20" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW19" s="1"/>
+    </row>
+    <row r="20" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -2352,8 +2913,9 @@
       <c r="AT20" s="1"/>
       <c r="AU20" s="1"/>
       <c r="AV20" s="1"/>
-    </row>
-    <row r="21" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW20" s="1"/>
+    </row>
+    <row r="21" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -2402,8 +2964,9 @@
       <c r="AT21" s="1"/>
       <c r="AU21" s="1"/>
       <c r="AV21" s="1"/>
-    </row>
-    <row r="22" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW21" s="1"/>
+    </row>
+    <row r="22" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -2452,8 +3015,9 @@
       <c r="AT22" s="1"/>
       <c r="AU22" s="1"/>
       <c r="AV22" s="1"/>
-    </row>
-    <row r="23" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW22" s="1"/>
+    </row>
+    <row r="23" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -2502,8 +3066,9 @@
       <c r="AT23" s="1"/>
       <c r="AU23" s="1"/>
       <c r="AV23" s="1"/>
-    </row>
-    <row r="24" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW23" s="1"/>
+    </row>
+    <row r="24" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -2552,8 +3117,9 @@
       <c r="AT24" s="1"/>
       <c r="AU24" s="1"/>
       <c r="AV24" s="1"/>
-    </row>
-    <row r="25" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW24" s="1"/>
+    </row>
+    <row r="25" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -2602,8 +3168,9 @@
       <c r="AT25" s="1"/>
       <c r="AU25" s="1"/>
       <c r="AV25" s="1"/>
-    </row>
-    <row r="26" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW25" s="1"/>
+    </row>
+    <row r="26" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -2652,8 +3219,9 @@
       <c r="AT26" s="1"/>
       <c r="AU26" s="1"/>
       <c r="AV26" s="1"/>
-    </row>
-    <row r="27" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW26" s="1"/>
+    </row>
+    <row r="27" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -2702,8 +3270,9 @@
       <c r="AT27" s="1"/>
       <c r="AU27" s="1"/>
       <c r="AV27" s="1"/>
-    </row>
-    <row r="28" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW27" s="1"/>
+    </row>
+    <row r="28" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -2752,8 +3321,9 @@
       <c r="AT28" s="1"/>
       <c r="AU28" s="1"/>
       <c r="AV28" s="1"/>
-    </row>
-    <row r="29" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW28" s="1"/>
+    </row>
+    <row r="29" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -2802,8 +3372,9 @@
       <c r="AT29" s="1"/>
       <c r="AU29" s="1"/>
       <c r="AV29" s="1"/>
-    </row>
-    <row r="30" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW29" s="1"/>
+    </row>
+    <row r="30" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -2852,8 +3423,9 @@
       <c r="AT30" s="1"/>
       <c r="AU30" s="1"/>
       <c r="AV30" s="1"/>
-    </row>
-    <row r="31" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW30" s="1"/>
+    </row>
+    <row r="31" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -2902,8 +3474,9 @@
       <c r="AT31" s="1"/>
       <c r="AU31" s="1"/>
       <c r="AV31" s="1"/>
-    </row>
-    <row r="32" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW31" s="1"/>
+    </row>
+    <row r="32" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -2952,8 +3525,9 @@
       <c r="AT32" s="1"/>
       <c r="AU32" s="1"/>
       <c r="AV32" s="1"/>
-    </row>
-    <row r="33" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW32" s="1"/>
+    </row>
+    <row r="33" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -3002,8 +3576,9 @@
       <c r="AT33" s="1"/>
       <c r="AU33" s="1"/>
       <c r="AV33" s="1"/>
-    </row>
-    <row r="34" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW33" s="1"/>
+    </row>
+    <row r="34" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -3052,8 +3627,9 @@
       <c r="AT34" s="1"/>
       <c r="AU34" s="1"/>
       <c r="AV34" s="1"/>
-    </row>
-    <row r="35" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW34" s="1"/>
+    </row>
+    <row r="35" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -3102,8 +3678,9 @@
       <c r="AT35" s="1"/>
       <c r="AU35" s="1"/>
       <c r="AV35" s="1"/>
-    </row>
-    <row r="36" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW35" s="1"/>
+    </row>
+    <row r="36" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -3152,8 +3729,9 @@
       <c r="AT36" s="1"/>
       <c r="AU36" s="1"/>
       <c r="AV36" s="1"/>
-    </row>
-    <row r="37" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW36" s="1"/>
+    </row>
+    <row r="37" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -3202,8 +3780,9 @@
       <c r="AT37" s="1"/>
       <c r="AU37" s="1"/>
       <c r="AV37" s="1"/>
-    </row>
-    <row r="38" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW37" s="1"/>
+    </row>
+    <row r="38" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -3252,8 +3831,9 @@
       <c r="AT38" s="1"/>
       <c r="AU38" s="1"/>
       <c r="AV38" s="1"/>
-    </row>
-    <row r="39" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW38" s="1"/>
+    </row>
+    <row r="39" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -3302,8 +3882,9 @@
       <c r="AT39" s="1"/>
       <c r="AU39" s="1"/>
       <c r="AV39" s="1"/>
-    </row>
-    <row r="40" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW39" s="1"/>
+    </row>
+    <row r="40" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -3352,8 +3933,9 @@
       <c r="AT40" s="1"/>
       <c r="AU40" s="1"/>
       <c r="AV40" s="1"/>
-    </row>
-    <row r="41" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW40" s="1"/>
+    </row>
+    <row r="41" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -3402,8 +3984,9 @@
       <c r="AT41" s="1"/>
       <c r="AU41" s="1"/>
       <c r="AV41" s="1"/>
-    </row>
-    <row r="42" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW41" s="1"/>
+    </row>
+    <row r="42" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -3452,8 +4035,9 @@
       <c r="AT42" s="1"/>
       <c r="AU42" s="1"/>
       <c r="AV42" s="1"/>
-    </row>
-    <row r="43" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW42" s="1"/>
+    </row>
+    <row r="43" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -3502,8 +4086,9 @@
       <c r="AT43" s="1"/>
       <c r="AU43" s="1"/>
       <c r="AV43" s="1"/>
-    </row>
-    <row r="44" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW43" s="1"/>
+    </row>
+    <row r="44" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -3552,8 +4137,9 @@
       <c r="AT44" s="1"/>
       <c r="AU44" s="1"/>
       <c r="AV44" s="1"/>
-    </row>
-    <row r="45" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW44" s="1"/>
+    </row>
+    <row r="45" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -3602,8 +4188,9 @@
       <c r="AT45" s="1"/>
       <c r="AU45" s="1"/>
       <c r="AV45" s="1"/>
-    </row>
-    <row r="46" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW45" s="1"/>
+    </row>
+    <row r="46" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -3652,8 +4239,9 @@
       <c r="AT46" s="1"/>
       <c r="AU46" s="1"/>
       <c r="AV46" s="1"/>
-    </row>
-    <row r="47" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW46" s="1"/>
+    </row>
+    <row r="47" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -3702,8 +4290,9 @@
       <c r="AT47" s="1"/>
       <c r="AU47" s="1"/>
       <c r="AV47" s="1"/>
-    </row>
-    <row r="48" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW47" s="1"/>
+    </row>
+    <row r="48" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -3752,8 +4341,9 @@
       <c r="AT48" s="1"/>
       <c r="AU48" s="1"/>
       <c r="AV48" s="1"/>
-    </row>
-    <row r="49" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW48" s="1"/>
+    </row>
+    <row r="49" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -3802,8 +4392,9 @@
       <c r="AT49" s="1"/>
       <c r="AU49" s="1"/>
       <c r="AV49" s="1"/>
-    </row>
-    <row r="50" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW49" s="1"/>
+    </row>
+    <row r="50" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -3852,8 +4443,9 @@
       <c r="AT50" s="1"/>
       <c r="AU50" s="1"/>
       <c r="AV50" s="1"/>
-    </row>
-    <row r="51" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW50" s="1"/>
+    </row>
+    <row r="51" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -3902,8 +4494,9 @@
       <c r="AT51" s="1"/>
       <c r="AU51" s="1"/>
       <c r="AV51" s="1"/>
-    </row>
-    <row r="52" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW51" s="1"/>
+    </row>
+    <row r="52" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -3952,8 +4545,9 @@
       <c r="AT52" s="1"/>
       <c r="AU52" s="1"/>
       <c r="AV52" s="1"/>
-    </row>
-    <row r="53" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW52" s="1"/>
+    </row>
+    <row r="53" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -4002,8 +4596,9 @@
       <c r="AT53" s="1"/>
       <c r="AU53" s="1"/>
       <c r="AV53" s="1"/>
-    </row>
-    <row r="54" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW53" s="1"/>
+    </row>
+    <row r="54" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -4052,8 +4647,9 @@
       <c r="AT54" s="1"/>
       <c r="AU54" s="1"/>
       <c r="AV54" s="1"/>
-    </row>
-    <row r="55" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW54" s="1"/>
+    </row>
+    <row r="55" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -4102,8 +4698,9 @@
       <c r="AT55" s="1"/>
       <c r="AU55" s="1"/>
       <c r="AV55" s="1"/>
-    </row>
-    <row r="56" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW55" s="1"/>
+    </row>
+    <row r="56" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -4152,8 +4749,9 @@
       <c r="AT56" s="1"/>
       <c r="AU56" s="1"/>
       <c r="AV56" s="1"/>
-    </row>
-    <row r="57" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW56" s="1"/>
+    </row>
+    <row r="57" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -4202,8 +4800,9 @@
       <c r="AT57" s="1"/>
       <c r="AU57" s="1"/>
       <c r="AV57" s="1"/>
-    </row>
-    <row r="58" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW57" s="1"/>
+    </row>
+    <row r="58" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -4252,8 +4851,9 @@
       <c r="AT58" s="1"/>
       <c r="AU58" s="1"/>
       <c r="AV58" s="1"/>
-    </row>
-    <row r="59" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW58" s="1"/>
+    </row>
+    <row r="59" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -4302,8 +4902,9 @@
       <c r="AT59" s="1"/>
       <c r="AU59" s="1"/>
       <c r="AV59" s="1"/>
-    </row>
-    <row r="60" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW59" s="1"/>
+    </row>
+    <row r="60" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -4352,8 +4953,9 @@
       <c r="AT60" s="1"/>
       <c r="AU60" s="1"/>
       <c r="AV60" s="1"/>
-    </row>
-    <row r="61" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW60" s="1"/>
+    </row>
+    <row r="61" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -4402,8 +5004,9 @@
       <c r="AT61" s="1"/>
       <c r="AU61" s="1"/>
       <c r="AV61" s="1"/>
-    </row>
-    <row r="62" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW61" s="1"/>
+    </row>
+    <row r="62" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -4452,8 +5055,9 @@
       <c r="AT62" s="1"/>
       <c r="AU62" s="1"/>
       <c r="AV62" s="1"/>
-    </row>
-    <row r="63" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW62" s="1"/>
+    </row>
+    <row r="63" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -4502,8 +5106,9 @@
       <c r="AT63" s="1"/>
       <c r="AU63" s="1"/>
       <c r="AV63" s="1"/>
-    </row>
-    <row r="64" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW63" s="1"/>
+    </row>
+    <row r="64" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -4552,8 +5157,9 @@
       <c r="AT64" s="1"/>
       <c r="AU64" s="1"/>
       <c r="AV64" s="1"/>
-    </row>
-    <row r="65" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW64" s="1"/>
+    </row>
+    <row r="65" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -4602,8 +5208,9 @@
       <c r="AT65" s="1"/>
       <c r="AU65" s="1"/>
       <c r="AV65" s="1"/>
-    </row>
-    <row r="66" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW65" s="1"/>
+    </row>
+    <row r="66" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
@@ -4652,8 +5259,9 @@
       <c r="AT66" s="1"/>
       <c r="AU66" s="1"/>
       <c r="AV66" s="1"/>
-    </row>
-    <row r="67" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW66" s="1"/>
+    </row>
+    <row r="67" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
@@ -4702,8 +5310,9 @@
       <c r="AT67" s="1"/>
       <c r="AU67" s="1"/>
       <c r="AV67" s="1"/>
-    </row>
-    <row r="68" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW67" s="1"/>
+    </row>
+    <row r="68" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -4752,8 +5361,9 @@
       <c r="AT68" s="1"/>
       <c r="AU68" s="1"/>
       <c r="AV68" s="1"/>
-    </row>
-    <row r="69" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW68" s="1"/>
+    </row>
+    <row r="69" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
@@ -4802,8 +5412,9 @@
       <c r="AT69" s="1"/>
       <c r="AU69" s="1"/>
       <c r="AV69" s="1"/>
-    </row>
-    <row r="70" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW69" s="1"/>
+    </row>
+    <row r="70" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
@@ -4852,8 +5463,9 @@
       <c r="AT70" s="1"/>
       <c r="AU70" s="1"/>
       <c r="AV70" s="1"/>
-    </row>
-    <row r="71" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW70" s="1"/>
+    </row>
+    <row r="71" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
@@ -4902,8 +5514,9 @@
       <c r="AT71" s="1"/>
       <c r="AU71" s="1"/>
       <c r="AV71" s="1"/>
-    </row>
-    <row r="72" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW71" s="1"/>
+    </row>
+    <row r="72" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
@@ -4952,8 +5565,9 @@
       <c r="AT72" s="1"/>
       <c r="AU72" s="1"/>
       <c r="AV72" s="1"/>
-    </row>
-    <row r="73" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW72" s="1"/>
+    </row>
+    <row r="73" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -5002,8 +5616,9 @@
       <c r="AT73" s="1"/>
       <c r="AU73" s="1"/>
       <c r="AV73" s="1"/>
-    </row>
-    <row r="74" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW73" s="1"/>
+    </row>
+    <row r="74" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -5052,8 +5667,9 @@
       <c r="AT74" s="1"/>
       <c r="AU74" s="1"/>
       <c r="AV74" s="1"/>
-    </row>
-    <row r="75" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW74" s="1"/>
+    </row>
+    <row r="75" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -5102,8 +5718,9 @@
       <c r="AT75" s="1"/>
       <c r="AU75" s="1"/>
       <c r="AV75" s="1"/>
-    </row>
-    <row r="76" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW75" s="1"/>
+    </row>
+    <row r="76" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -5152,8 +5769,9 @@
       <c r="AT76" s="1"/>
       <c r="AU76" s="1"/>
       <c r="AV76" s="1"/>
-    </row>
-    <row r="77" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW76" s="1"/>
+    </row>
+    <row r="77" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
@@ -5202,8 +5820,9 @@
       <c r="AT77" s="1"/>
       <c r="AU77" s="1"/>
       <c r="AV77" s="1"/>
-    </row>
-    <row r="78" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW77" s="1"/>
+    </row>
+    <row r="78" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -5252,8 +5871,9 @@
       <c r="AT78" s="1"/>
       <c r="AU78" s="1"/>
       <c r="AV78" s="1"/>
-    </row>
-    <row r="79" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW78" s="1"/>
+    </row>
+    <row r="79" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -5302,8 +5922,9 @@
       <c r="AT79" s="1"/>
       <c r="AU79" s="1"/>
       <c r="AV79" s="1"/>
-    </row>
-    <row r="80" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW79" s="1"/>
+    </row>
+    <row r="80" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -5352,8 +5973,9 @@
       <c r="AT80" s="1"/>
       <c r="AU80" s="1"/>
       <c r="AV80" s="1"/>
-    </row>
-    <row r="81" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW80" s="1"/>
+    </row>
+    <row r="81" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -5402,8 +6024,9 @@
       <c r="AT81" s="1"/>
       <c r="AU81" s="1"/>
       <c r="AV81" s="1"/>
-    </row>
-    <row r="82" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW81" s="1"/>
+    </row>
+    <row r="82" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -5452,8 +6075,9 @@
       <c r="AT82" s="1"/>
       <c r="AU82" s="1"/>
       <c r="AV82" s="1"/>
-    </row>
-    <row r="83" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW82" s="1"/>
+    </row>
+    <row r="83" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -5502,8 +6126,9 @@
       <c r="AT83" s="1"/>
       <c r="AU83" s="1"/>
       <c r="AV83" s="1"/>
-    </row>
-    <row r="84" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW83" s="1"/>
+    </row>
+    <row r="84" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -5552,8 +6177,9 @@
       <c r="AT84" s="1"/>
       <c r="AU84" s="1"/>
       <c r="AV84" s="1"/>
-    </row>
-    <row r="85" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW84" s="1"/>
+    </row>
+    <row r="85" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -5602,8 +6228,9 @@
       <c r="AT85" s="1"/>
       <c r="AU85" s="1"/>
       <c r="AV85" s="1"/>
-    </row>
-    <row r="86" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW85" s="1"/>
+    </row>
+    <row r="86" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -5652,8 +6279,9 @@
       <c r="AT86" s="1"/>
       <c r="AU86" s="1"/>
       <c r="AV86" s="1"/>
-    </row>
-    <row r="87" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW86" s="1"/>
+    </row>
+    <row r="87" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -5702,8 +6330,9 @@
       <c r="AT87" s="1"/>
       <c r="AU87" s="1"/>
       <c r="AV87" s="1"/>
-    </row>
-    <row r="88" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW87" s="1"/>
+    </row>
+    <row r="88" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -5752,8 +6381,9 @@
       <c r="AT88" s="1"/>
       <c r="AU88" s="1"/>
       <c r="AV88" s="1"/>
-    </row>
-    <row r="89" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW88" s="1"/>
+    </row>
+    <row r="89" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -5802,8 +6432,9 @@
       <c r="AT89" s="1"/>
       <c r="AU89" s="1"/>
       <c r="AV89" s="1"/>
-    </row>
-    <row r="90" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW89" s="1"/>
+    </row>
+    <row r="90" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -5852,8 +6483,9 @@
       <c r="AT90" s="1"/>
       <c r="AU90" s="1"/>
       <c r="AV90" s="1"/>
-    </row>
-    <row r="91" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW90" s="1"/>
+    </row>
+    <row r="91" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -5902,8 +6534,9 @@
       <c r="AT91" s="1"/>
       <c r="AU91" s="1"/>
       <c r="AV91" s="1"/>
-    </row>
-    <row r="92" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW91" s="1"/>
+    </row>
+    <row r="92" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -5952,8 +6585,9 @@
       <c r="AT92" s="1"/>
       <c r="AU92" s="1"/>
       <c r="AV92" s="1"/>
-    </row>
-    <row r="93" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW92" s="1"/>
+    </row>
+    <row r="93" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -6002,8 +6636,9 @@
       <c r="AT93" s="1"/>
       <c r="AU93" s="1"/>
       <c r="AV93" s="1"/>
-    </row>
-    <row r="94" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW93" s="1"/>
+    </row>
+    <row r="94" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -6052,8 +6687,9 @@
       <c r="AT94" s="1"/>
       <c r="AU94" s="1"/>
       <c r="AV94" s="1"/>
-    </row>
-    <row r="95" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW94" s="1"/>
+    </row>
+    <row r="95" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -6102,8 +6738,9 @@
       <c r="AT95" s="1"/>
       <c r="AU95" s="1"/>
       <c r="AV95" s="1"/>
-    </row>
-    <row r="96" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW95" s="1"/>
+    </row>
+    <row r="96" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -6152,8 +6789,9 @@
       <c r="AT96" s="1"/>
       <c r="AU96" s="1"/>
       <c r="AV96" s="1"/>
-    </row>
-    <row r="97" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW96" s="1"/>
+    </row>
+    <row r="97" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -6202,8 +6840,9 @@
       <c r="AT97" s="1"/>
       <c r="AU97" s="1"/>
       <c r="AV97" s="1"/>
-    </row>
-    <row r="98" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW97" s="1"/>
+    </row>
+    <row r="98" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -6252,8 +6891,9 @@
       <c r="AT98" s="1"/>
       <c r="AU98" s="1"/>
       <c r="AV98" s="1"/>
-    </row>
-    <row r="99" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW98" s="1"/>
+    </row>
+    <row r="99" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -6302,8 +6942,9 @@
       <c r="AT99" s="1"/>
       <c r="AU99" s="1"/>
       <c r="AV99" s="1"/>
-    </row>
-    <row r="100" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW99" s="1"/>
+    </row>
+    <row r="100" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -6352,8 +6993,9 @@
       <c r="AT100" s="1"/>
       <c r="AU100" s="1"/>
       <c r="AV100" s="1"/>
-    </row>
-    <row r="101" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW100" s="1"/>
+    </row>
+    <row r="101" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -6402,8 +7044,9 @@
       <c r="AT101" s="1"/>
       <c r="AU101" s="1"/>
       <c r="AV101" s="1"/>
-    </row>
-    <row r="102" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW101" s="1"/>
+    </row>
+    <row r="102" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -6452,8 +7095,9 @@
       <c r="AT102" s="1"/>
       <c r="AU102" s="1"/>
       <c r="AV102" s="1"/>
-    </row>
-    <row r="103" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW102" s="1"/>
+    </row>
+    <row r="103" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -6502,8 +7146,9 @@
       <c r="AT103" s="1"/>
       <c r="AU103" s="1"/>
       <c r="AV103" s="1"/>
-    </row>
-    <row r="104" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW103" s="1"/>
+    </row>
+    <row r="104" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -6552,8 +7197,9 @@
       <c r="AT104" s="1"/>
       <c r="AU104" s="1"/>
       <c r="AV104" s="1"/>
-    </row>
-    <row r="105" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW104" s="1"/>
+    </row>
+    <row r="105" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -6602,8 +7248,9 @@
       <c r="AT105" s="1"/>
       <c r="AU105" s="1"/>
       <c r="AV105" s="1"/>
-    </row>
-    <row r="106" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW105" s="1"/>
+    </row>
+    <row r="106" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -6652,8 +7299,9 @@
       <c r="AT106" s="1"/>
       <c r="AU106" s="1"/>
       <c r="AV106" s="1"/>
-    </row>
-    <row r="107" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW106" s="1"/>
+    </row>
+    <row r="107" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -6702,8 +7350,9 @@
       <c r="AT107" s="1"/>
       <c r="AU107" s="1"/>
       <c r="AV107" s="1"/>
-    </row>
-    <row r="108" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW107" s="1"/>
+    </row>
+    <row r="108" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -6752,8 +7401,9 @@
       <c r="AT108" s="1"/>
       <c r="AU108" s="1"/>
       <c r="AV108" s="1"/>
-    </row>
-    <row r="109" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW108" s="1"/>
+    </row>
+    <row r="109" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -6802,8 +7452,9 @@
       <c r="AT109" s="1"/>
       <c r="AU109" s="1"/>
       <c r="AV109" s="1"/>
-    </row>
-    <row r="110" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW109" s="1"/>
+    </row>
+    <row r="110" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -6852,8 +7503,9 @@
       <c r="AT110" s="1"/>
       <c r="AU110" s="1"/>
       <c r="AV110" s="1"/>
-    </row>
-    <row r="111" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW110" s="1"/>
+    </row>
+    <row r="111" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -6902,8 +7554,9 @@
       <c r="AT111" s="1"/>
       <c r="AU111" s="1"/>
       <c r="AV111" s="1"/>
-    </row>
-    <row r="112" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW111" s="1"/>
+    </row>
+    <row r="112" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -6952,8 +7605,9 @@
       <c r="AT112" s="1"/>
       <c r="AU112" s="1"/>
       <c r="AV112" s="1"/>
-    </row>
-    <row r="113" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW112" s="1"/>
+    </row>
+    <row r="113" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -7002,8 +7656,9 @@
       <c r="AT113" s="1"/>
       <c r="AU113" s="1"/>
       <c r="AV113" s="1"/>
-    </row>
-    <row r="114" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW113" s="1"/>
+    </row>
+    <row r="114" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -7052,8 +7707,9 @@
       <c r="AT114" s="1"/>
       <c r="AU114" s="1"/>
       <c r="AV114" s="1"/>
-    </row>
-    <row r="115" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW114" s="1"/>
+    </row>
+    <row r="115" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -7102,8 +7758,9 @@
       <c r="AT115" s="1"/>
       <c r="AU115" s="1"/>
       <c r="AV115" s="1"/>
-    </row>
-    <row r="116" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW115" s="1"/>
+    </row>
+    <row r="116" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -7152,8 +7809,9 @@
       <c r="AT116" s="1"/>
       <c r="AU116" s="1"/>
       <c r="AV116" s="1"/>
-    </row>
-    <row r="117" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW116" s="1"/>
+    </row>
+    <row r="117" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -7202,8 +7860,9 @@
       <c r="AT117" s="1"/>
       <c r="AU117" s="1"/>
       <c r="AV117" s="1"/>
-    </row>
-    <row r="118" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW117" s="1"/>
+    </row>
+    <row r="118" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -7252,8 +7911,9 @@
       <c r="AT118" s="1"/>
       <c r="AU118" s="1"/>
       <c r="AV118" s="1"/>
-    </row>
-    <row r="119" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW118" s="1"/>
+    </row>
+    <row r="119" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -7302,8 +7962,9 @@
       <c r="AT119" s="1"/>
       <c r="AU119" s="1"/>
       <c r="AV119" s="1"/>
-    </row>
-    <row r="120" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW119" s="1"/>
+    </row>
+    <row r="120" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -7352,8 +8013,9 @@
       <c r="AT120" s="1"/>
       <c r="AU120" s="1"/>
       <c r="AV120" s="1"/>
-    </row>
-    <row r="121" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW120" s="1"/>
+    </row>
+    <row r="121" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -7402,8 +8064,9 @@
       <c r="AT121" s="1"/>
       <c r="AU121" s="1"/>
       <c r="AV121" s="1"/>
-    </row>
-    <row r="122" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW121" s="1"/>
+    </row>
+    <row r="122" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -7452,8 +8115,9 @@
       <c r="AT122" s="1"/>
       <c r="AU122" s="1"/>
       <c r="AV122" s="1"/>
-    </row>
-    <row r="123" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW122" s="1"/>
+    </row>
+    <row r="123" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -7502,8 +8166,9 @@
       <c r="AT123" s="1"/>
       <c r="AU123" s="1"/>
       <c r="AV123" s="1"/>
-    </row>
-    <row r="124" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW123" s="1"/>
+    </row>
+    <row r="124" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -7552,8 +8217,9 @@
       <c r="AT124" s="1"/>
       <c r="AU124" s="1"/>
       <c r="AV124" s="1"/>
-    </row>
-    <row r="125" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW124" s="1"/>
+    </row>
+    <row r="125" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -7602,8 +8268,9 @@
       <c r="AT125" s="1"/>
       <c r="AU125" s="1"/>
       <c r="AV125" s="1"/>
-    </row>
-    <row r="126" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW125" s="1"/>
+    </row>
+    <row r="126" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -7652,8 +8319,9 @@
       <c r="AT126" s="1"/>
       <c r="AU126" s="1"/>
       <c r="AV126" s="1"/>
-    </row>
-    <row r="127" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW126" s="1"/>
+    </row>
+    <row r="127" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -7702,8 +8370,9 @@
       <c r="AT127" s="1"/>
       <c r="AU127" s="1"/>
       <c r="AV127" s="1"/>
-    </row>
-    <row r="128" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW127" s="1"/>
+    </row>
+    <row r="128" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -7752,8 +8421,9 @@
       <c r="AT128" s="1"/>
       <c r="AU128" s="1"/>
       <c r="AV128" s="1"/>
-    </row>
-    <row r="129" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW128" s="1"/>
+    </row>
+    <row r="129" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -7802,8 +8472,9 @@
       <c r="AT129" s="1"/>
       <c r="AU129" s="1"/>
       <c r="AV129" s="1"/>
-    </row>
-    <row r="130" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW129" s="1"/>
+    </row>
+    <row r="130" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -7852,8 +8523,9 @@
       <c r="AT130" s="1"/>
       <c r="AU130" s="1"/>
       <c r="AV130" s="1"/>
-    </row>
-    <row r="131" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW130" s="1"/>
+    </row>
+    <row r="131" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
@@ -7902,8 +8574,9 @@
       <c r="AT131" s="1"/>
       <c r="AU131" s="1"/>
       <c r="AV131" s="1"/>
-    </row>
-    <row r="132" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW131" s="1"/>
+    </row>
+    <row r="132" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
@@ -7952,8 +8625,9 @@
       <c r="AT132" s="1"/>
       <c r="AU132" s="1"/>
       <c r="AV132" s="1"/>
-    </row>
-    <row r="133" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW132" s="1"/>
+    </row>
+    <row r="133" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -8002,8 +8676,9 @@
       <c r="AT133" s="1"/>
       <c r="AU133" s="1"/>
       <c r="AV133" s="1"/>
-    </row>
-    <row r="134" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW133" s="1"/>
+    </row>
+    <row r="134" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
@@ -8052,8 +8727,9 @@
       <c r="AT134" s="1"/>
       <c r="AU134" s="1"/>
       <c r="AV134" s="1"/>
-    </row>
-    <row r="135" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW134" s="1"/>
+    </row>
+    <row r="135" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -8102,8 +8778,9 @@
       <c r="AT135" s="1"/>
       <c r="AU135" s="1"/>
       <c r="AV135" s="1"/>
-    </row>
-    <row r="136" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW135" s="1"/>
+    </row>
+    <row r="136" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -8152,8 +8829,9 @@
       <c r="AT136" s="1"/>
       <c r="AU136" s="1"/>
       <c r="AV136" s="1"/>
-    </row>
-    <row r="137" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW136" s="1"/>
+    </row>
+    <row r="137" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
@@ -8202,8 +8880,9 @@
       <c r="AT137" s="1"/>
       <c r="AU137" s="1"/>
       <c r="AV137" s="1"/>
-    </row>
-    <row r="138" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW137" s="1"/>
+    </row>
+    <row r="138" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
@@ -8252,8 +8931,9 @@
       <c r="AT138" s="1"/>
       <c r="AU138" s="1"/>
       <c r="AV138" s="1"/>
-    </row>
-    <row r="139" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW138" s="1"/>
+    </row>
+    <row r="139" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
@@ -8302,8 +8982,9 @@
       <c r="AT139" s="1"/>
       <c r="AU139" s="1"/>
       <c r="AV139" s="1"/>
-    </row>
-    <row r="140" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW139" s="1"/>
+    </row>
+    <row r="140" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
@@ -8352,8 +9033,9 @@
       <c r="AT140" s="1"/>
       <c r="AU140" s="1"/>
       <c r="AV140" s="1"/>
-    </row>
-    <row r="141" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW140" s="1"/>
+    </row>
+    <row r="141" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
@@ -8402,8 +9084,9 @@
       <c r="AT141" s="1"/>
       <c r="AU141" s="1"/>
       <c r="AV141" s="1"/>
-    </row>
-    <row r="142" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW141" s="1"/>
+    </row>
+    <row r="142" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
@@ -8452,8 +9135,9 @@
       <c r="AT142" s="1"/>
       <c r="AU142" s="1"/>
       <c r="AV142" s="1"/>
-    </row>
-    <row r="143" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW142" s="1"/>
+    </row>
+    <row r="143" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
@@ -8502,8 +9186,9 @@
       <c r="AT143" s="1"/>
       <c r="AU143" s="1"/>
       <c r="AV143" s="1"/>
-    </row>
-    <row r="144" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW143" s="1"/>
+    </row>
+    <row r="144" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
@@ -8552,8 +9237,9 @@
       <c r="AT144" s="1"/>
       <c r="AU144" s="1"/>
       <c r="AV144" s="1"/>
-    </row>
-    <row r="145" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW144" s="1"/>
+    </row>
+    <row r="145" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
@@ -8602,8 +9288,9 @@
       <c r="AT145" s="1"/>
       <c r="AU145" s="1"/>
       <c r="AV145" s="1"/>
-    </row>
-    <row r="146" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW145" s="1"/>
+    </row>
+    <row r="146" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
@@ -8652,8 +9339,9 @@
       <c r="AT146" s="1"/>
       <c r="AU146" s="1"/>
       <c r="AV146" s="1"/>
-    </row>
-    <row r="147" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW146" s="1"/>
+    </row>
+    <row r="147" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
@@ -8702,8 +9390,9 @@
       <c r="AT147" s="1"/>
       <c r="AU147" s="1"/>
       <c r="AV147" s="1"/>
-    </row>
-    <row r="148" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW147" s="1"/>
+    </row>
+    <row r="148" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
@@ -8752,8 +9441,9 @@
       <c r="AT148" s="1"/>
       <c r="AU148" s="1"/>
       <c r="AV148" s="1"/>
-    </row>
-    <row r="149" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW148" s="1"/>
+    </row>
+    <row r="149" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
@@ -8802,8 +9492,9 @@
       <c r="AT149" s="1"/>
       <c r="AU149" s="1"/>
       <c r="AV149" s="1"/>
-    </row>
-    <row r="150" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW149" s="1"/>
+    </row>
+    <row r="150" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -8852,8 +9543,9 @@
       <c r="AT150" s="1"/>
       <c r="AU150" s="1"/>
       <c r="AV150" s="1"/>
-    </row>
-    <row r="151" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW150" s="1"/>
+    </row>
+    <row r="151" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
@@ -8902,8 +9594,9 @@
       <c r="AT151" s="1"/>
       <c r="AU151" s="1"/>
       <c r="AV151" s="1"/>
-    </row>
-    <row r="152" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW151" s="1"/>
+    </row>
+    <row r="152" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
@@ -8952,8 +9645,9 @@
       <c r="AT152" s="1"/>
       <c r="AU152" s="1"/>
       <c r="AV152" s="1"/>
-    </row>
-    <row r="153" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW152" s="1"/>
+    </row>
+    <row r="153" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
@@ -9002,8 +9696,9 @@
       <c r="AT153" s="1"/>
       <c r="AU153" s="1"/>
       <c r="AV153" s="1"/>
-    </row>
-    <row r="154" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW153" s="1"/>
+    </row>
+    <row r="154" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
@@ -9052,8 +9747,9 @@
       <c r="AT154" s="1"/>
       <c r="AU154" s="1"/>
       <c r="AV154" s="1"/>
-    </row>
-    <row r="155" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW154" s="1"/>
+    </row>
+    <row r="155" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
@@ -9102,8 +9798,9 @@
       <c r="AT155" s="1"/>
       <c r="AU155" s="1"/>
       <c r="AV155" s="1"/>
-    </row>
-    <row r="156" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW155" s="1"/>
+    </row>
+    <row r="156" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -9152,8 +9849,9 @@
       <c r="AT156" s="1"/>
       <c r="AU156" s="1"/>
       <c r="AV156" s="1"/>
-    </row>
-    <row r="157" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW156" s="1"/>
+    </row>
+    <row r="157" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -9202,8 +9900,9 @@
       <c r="AT157" s="1"/>
       <c r="AU157" s="1"/>
       <c r="AV157" s="1"/>
-    </row>
-    <row r="158" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW157" s="1"/>
+    </row>
+    <row r="158" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
@@ -9252,8 +9951,9 @@
       <c r="AT158" s="1"/>
       <c r="AU158" s="1"/>
       <c r="AV158" s="1"/>
-    </row>
-    <row r="159" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW158" s="1"/>
+    </row>
+    <row r="159" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
@@ -9302,8 +10002,9 @@
       <c r="AT159" s="1"/>
       <c r="AU159" s="1"/>
       <c r="AV159" s="1"/>
-    </row>
-    <row r="160" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW159" s="1"/>
+    </row>
+    <row r="160" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -9352,8 +10053,9 @@
       <c r="AT160" s="1"/>
       <c r="AU160" s="1"/>
       <c r="AV160" s="1"/>
-    </row>
-    <row r="161" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW160" s="1"/>
+    </row>
+    <row r="161" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -9402,8 +10104,9 @@
       <c r="AT161" s="1"/>
       <c r="AU161" s="1"/>
       <c r="AV161" s="1"/>
-    </row>
-    <row r="162" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW161" s="1"/>
+    </row>
+    <row r="162" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -9452,8 +10155,9 @@
       <c r="AT162" s="1"/>
       <c r="AU162" s="1"/>
       <c r="AV162" s="1"/>
-    </row>
-    <row r="163" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW162" s="1"/>
+    </row>
+    <row r="163" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
@@ -9502,8 +10206,9 @@
       <c r="AT163" s="1"/>
       <c r="AU163" s="1"/>
       <c r="AV163" s="1"/>
-    </row>
-    <row r="164" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW163" s="1"/>
+    </row>
+    <row r="164" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
@@ -9552,8 +10257,9 @@
       <c r="AT164" s="1"/>
       <c r="AU164" s="1"/>
       <c r="AV164" s="1"/>
-    </row>
-    <row r="165" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW164" s="1"/>
+    </row>
+    <row r="165" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
@@ -9602,8 +10308,9 @@
       <c r="AT165" s="1"/>
       <c r="AU165" s="1"/>
       <c r="AV165" s="1"/>
-    </row>
-    <row r="166" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW165" s="1"/>
+    </row>
+    <row r="166" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
@@ -9652,8 +10359,9 @@
       <c r="AT166" s="1"/>
       <c r="AU166" s="1"/>
       <c r="AV166" s="1"/>
-    </row>
-    <row r="167" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW166" s="1"/>
+    </row>
+    <row r="167" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="1"/>
@@ -9702,8 +10410,9 @@
       <c r="AT167" s="1"/>
       <c r="AU167" s="1"/>
       <c r="AV167" s="1"/>
-    </row>
-    <row r="168" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW167" s="1"/>
+    </row>
+    <row r="168" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
@@ -9752,8 +10461,9 @@
       <c r="AT168" s="1"/>
       <c r="AU168" s="1"/>
       <c r="AV168" s="1"/>
-    </row>
-    <row r="169" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW168" s="1"/>
+    </row>
+    <row r="169" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
@@ -9802,8 +10512,9 @@
       <c r="AT169" s="1"/>
       <c r="AU169" s="1"/>
       <c r="AV169" s="1"/>
-    </row>
-    <row r="170" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW169" s="1"/>
+    </row>
+    <row r="170" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="1"/>
@@ -9852,8 +10563,9 @@
       <c r="AT170" s="1"/>
       <c r="AU170" s="1"/>
       <c r="AV170" s="1"/>
-    </row>
-    <row r="171" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW170" s="1"/>
+    </row>
+    <row r="171" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="1"/>
@@ -9902,8 +10614,9 @@
       <c r="AT171" s="1"/>
       <c r="AU171" s="1"/>
       <c r="AV171" s="1"/>
-    </row>
-    <row r="172" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW171" s="1"/>
+    </row>
+    <row r="172" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="1"/>
@@ -9952,8 +10665,9 @@
       <c r="AT172" s="1"/>
       <c r="AU172" s="1"/>
       <c r="AV172" s="1"/>
-    </row>
-    <row r="173" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW172" s="1"/>
+    </row>
+    <row r="173" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
@@ -10002,8 +10716,9 @@
       <c r="AT173" s="1"/>
       <c r="AU173" s="1"/>
       <c r="AV173" s="1"/>
-    </row>
-    <row r="174" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW173" s="1"/>
+    </row>
+    <row r="174" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
@@ -10052,8 +10767,9 @@
       <c r="AT174" s="1"/>
       <c r="AU174" s="1"/>
       <c r="AV174" s="1"/>
-    </row>
-    <row r="175" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW174" s="1"/>
+    </row>
+    <row r="175" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
@@ -10102,8 +10818,9 @@
       <c r="AT175" s="1"/>
       <c r="AU175" s="1"/>
       <c r="AV175" s="1"/>
-    </row>
-    <row r="176" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW175" s="1"/>
+    </row>
+    <row r="176" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
@@ -10152,8 +10869,9 @@
       <c r="AT176" s="1"/>
       <c r="AU176" s="1"/>
       <c r="AV176" s="1"/>
-    </row>
-    <row r="177" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW176" s="1"/>
+    </row>
+    <row r="177" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
@@ -10202,8 +10920,9 @@
       <c r="AT177" s="1"/>
       <c r="AU177" s="1"/>
       <c r="AV177" s="1"/>
-    </row>
-    <row r="178" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW177" s="1"/>
+    </row>
+    <row r="178" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
@@ -10252,8 +10971,9 @@
       <c r="AT178" s="1"/>
       <c r="AU178" s="1"/>
       <c r="AV178" s="1"/>
-    </row>
-    <row r="179" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW178" s="1"/>
+    </row>
+    <row r="179" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
@@ -10302,8 +11022,9 @@
       <c r="AT179" s="1"/>
       <c r="AU179" s="1"/>
       <c r="AV179" s="1"/>
-    </row>
-    <row r="180" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW179" s="1"/>
+    </row>
+    <row r="180" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
@@ -10352,8 +11073,9 @@
       <c r="AT180" s="1"/>
       <c r="AU180" s="1"/>
       <c r="AV180" s="1"/>
-    </row>
-    <row r="181" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW180" s="1"/>
+    </row>
+    <row r="181" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
@@ -10402,8 +11124,9 @@
       <c r="AT181" s="1"/>
       <c r="AU181" s="1"/>
       <c r="AV181" s="1"/>
-    </row>
-    <row r="182" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW181" s="1"/>
+    </row>
+    <row r="182" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
@@ -10452,8 +11175,9 @@
       <c r="AT182" s="1"/>
       <c r="AU182" s="1"/>
       <c r="AV182" s="1"/>
-    </row>
-    <row r="183" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW182" s="1"/>
+    </row>
+    <row r="183" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="1"/>
@@ -10502,8 +11226,9 @@
       <c r="AT183" s="1"/>
       <c r="AU183" s="1"/>
       <c r="AV183" s="1"/>
-    </row>
-    <row r="184" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW183" s="1"/>
+    </row>
+    <row r="184" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
@@ -10552,8 +11277,9 @@
       <c r="AT184" s="1"/>
       <c r="AU184" s="1"/>
       <c r="AV184" s="1"/>
-    </row>
-    <row r="185" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW184" s="1"/>
+    </row>
+    <row r="185" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
@@ -10602,8 +11328,9 @@
       <c r="AT185" s="1"/>
       <c r="AU185" s="1"/>
       <c r="AV185" s="1"/>
-    </row>
-    <row r="186" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW185" s="1"/>
+    </row>
+    <row r="186" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
@@ -10652,8 +11379,9 @@
       <c r="AT186" s="1"/>
       <c r="AU186" s="1"/>
       <c r="AV186" s="1"/>
-    </row>
-    <row r="187" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW186" s="1"/>
+    </row>
+    <row r="187" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="1"/>
@@ -10702,8 +11430,9 @@
       <c r="AT187" s="1"/>
       <c r="AU187" s="1"/>
       <c r="AV187" s="1"/>
-    </row>
-    <row r="188" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW187" s="1"/>
+    </row>
+    <row r="188" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
@@ -10752,8 +11481,9 @@
       <c r="AT188" s="1"/>
       <c r="AU188" s="1"/>
       <c r="AV188" s="1"/>
-    </row>
-    <row r="189" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW188" s="1"/>
+    </row>
+    <row r="189" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
@@ -10802,8 +11532,9 @@
       <c r="AT189" s="1"/>
       <c r="AU189" s="1"/>
       <c r="AV189" s="1"/>
-    </row>
-    <row r="190" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW189" s="1"/>
+    </row>
+    <row r="190" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
@@ -10852,8 +11583,9 @@
       <c r="AT190" s="1"/>
       <c r="AU190" s="1"/>
       <c r="AV190" s="1"/>
-    </row>
-    <row r="191" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW190" s="1"/>
+    </row>
+    <row r="191" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
@@ -10902,8 +11634,9 @@
       <c r="AT191" s="1"/>
       <c r="AU191" s="1"/>
       <c r="AV191" s="1"/>
-    </row>
-    <row r="192" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW191" s="1"/>
+    </row>
+    <row r="192" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="1"/>
@@ -10952,8 +11685,9 @@
       <c r="AT192" s="1"/>
       <c r="AU192" s="1"/>
       <c r="AV192" s="1"/>
-    </row>
-    <row r="193" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW192" s="1"/>
+    </row>
+    <row r="193" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
@@ -11002,8 +11736,9 @@
       <c r="AT193" s="1"/>
       <c r="AU193" s="1"/>
       <c r="AV193" s="1"/>
-    </row>
-    <row r="194" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW193" s="1"/>
+    </row>
+    <row r="194" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="1"/>
@@ -11052,8 +11787,9 @@
       <c r="AT194" s="1"/>
       <c r="AU194" s="1"/>
       <c r="AV194" s="1"/>
-    </row>
-    <row r="195" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW194" s="1"/>
+    </row>
+    <row r="195" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
@@ -11102,8 +11838,9 @@
       <c r="AT195" s="1"/>
       <c r="AU195" s="1"/>
       <c r="AV195" s="1"/>
-    </row>
-    <row r="196" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW195" s="1"/>
+    </row>
+    <row r="196" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="C196" s="1"/>
@@ -11152,8 +11889,9 @@
       <c r="AT196" s="1"/>
       <c r="AU196" s="1"/>
       <c r="AV196" s="1"/>
-    </row>
-    <row r="197" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW196" s="1"/>
+    </row>
+    <row r="197" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
       <c r="C197" s="1"/>
@@ -11202,8 +11940,9 @@
       <c r="AT197" s="1"/>
       <c r="AU197" s="1"/>
       <c r="AV197" s="1"/>
-    </row>
-    <row r="198" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW197" s="1"/>
+    </row>
+    <row r="198" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A198" s="1"/>
       <c r="B198" s="1"/>
       <c r="C198" s="1"/>
@@ -11252,8 +11991,9 @@
       <c r="AT198" s="1"/>
       <c r="AU198" s="1"/>
       <c r="AV198" s="1"/>
-    </row>
-    <row r="199" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW198" s="1"/>
+    </row>
+    <row r="199" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A199" s="1"/>
       <c r="B199" s="1"/>
       <c r="C199" s="1"/>
@@ -11302,8 +12042,9 @@
       <c r="AT199" s="1"/>
       <c r="AU199" s="1"/>
       <c r="AV199" s="1"/>
-    </row>
-    <row r="200" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW199" s="1"/>
+    </row>
+    <row r="200" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A200" s="1"/>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
@@ -11352,8 +12093,9 @@
       <c r="AT200" s="1"/>
       <c r="AU200" s="1"/>
       <c r="AV200" s="1"/>
-    </row>
-    <row r="201" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW200" s="1"/>
+    </row>
+    <row r="201" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A201" s="1"/>
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
@@ -11402,8 +12144,9 @@
       <c r="AT201" s="1"/>
       <c r="AU201" s="1"/>
       <c r="AV201" s="1"/>
-    </row>
-    <row r="202" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW201" s="1"/>
+    </row>
+    <row r="202" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A202" s="1"/>
       <c r="B202" s="1"/>
       <c r="C202" s="1"/>
@@ -11452,8 +12195,9 @@
       <c r="AT202" s="1"/>
       <c r="AU202" s="1"/>
       <c r="AV202" s="1"/>
-    </row>
-    <row r="203" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW202" s="1"/>
+    </row>
+    <row r="203" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A203" s="1"/>
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
@@ -11502,8 +12246,9 @@
       <c r="AT203" s="1"/>
       <c r="AU203" s="1"/>
       <c r="AV203" s="1"/>
-    </row>
-    <row r="204" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW203" s="1"/>
+    </row>
+    <row r="204" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
@@ -11552,8 +12297,9 @@
       <c r="AT204" s="1"/>
       <c r="AU204" s="1"/>
       <c r="AV204" s="1"/>
-    </row>
-    <row r="205" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW204" s="1"/>
+    </row>
+    <row r="205" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A205" s="1"/>
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
@@ -11602,8 +12348,9 @@
       <c r="AT205" s="1"/>
       <c r="AU205" s="1"/>
       <c r="AV205" s="1"/>
-    </row>
-    <row r="206" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW205" s="1"/>
+    </row>
+    <row r="206" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A206" s="1"/>
       <c r="B206" s="1"/>
       <c r="C206" s="1"/>
@@ -11652,8 +12399,9 @@
       <c r="AT206" s="1"/>
       <c r="AU206" s="1"/>
       <c r="AV206" s="1"/>
-    </row>
-    <row r="207" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW206" s="1"/>
+    </row>
+    <row r="207" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A207" s="1"/>
       <c r="B207" s="1"/>
       <c r="C207" s="1"/>
@@ -11702,8 +12450,9 @@
       <c r="AT207" s="1"/>
       <c r="AU207" s="1"/>
       <c r="AV207" s="1"/>
-    </row>
-    <row r="208" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW207" s="1"/>
+    </row>
+    <row r="208" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A208" s="1"/>
       <c r="B208" s="1"/>
       <c r="C208" s="1"/>
@@ -11752,8 +12501,9 @@
       <c r="AT208" s="1"/>
       <c r="AU208" s="1"/>
       <c r="AV208" s="1"/>
-    </row>
-    <row r="209" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW208" s="1"/>
+    </row>
+    <row r="209" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A209" s="1"/>
       <c r="B209" s="1"/>
       <c r="C209" s="1"/>
@@ -11802,8 +12552,9 @@
       <c r="AT209" s="1"/>
       <c r="AU209" s="1"/>
       <c r="AV209" s="1"/>
-    </row>
-    <row r="210" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW209" s="1"/>
+    </row>
+    <row r="210" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A210" s="1"/>
       <c r="B210" s="1"/>
       <c r="C210" s="1"/>
@@ -11852,8 +12603,9 @@
       <c r="AT210" s="1"/>
       <c r="AU210" s="1"/>
       <c r="AV210" s="1"/>
-    </row>
-    <row r="211" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW210" s="1"/>
+    </row>
+    <row r="211" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
       <c r="C211" s="1"/>
@@ -11902,8 +12654,9 @@
       <c r="AT211" s="1"/>
       <c r="AU211" s="1"/>
       <c r="AV211" s="1"/>
-    </row>
-    <row r="212" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW211" s="1"/>
+    </row>
+    <row r="212" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A212" s="1"/>
       <c r="B212" s="1"/>
       <c r="C212" s="1"/>
@@ -11952,8 +12705,9 @@
       <c r="AT212" s="1"/>
       <c r="AU212" s="1"/>
       <c r="AV212" s="1"/>
-    </row>
-    <row r="213" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW212" s="1"/>
+    </row>
+    <row r="213" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A213" s="1"/>
       <c r="B213" s="1"/>
       <c r="C213" s="1"/>
@@ -12002,8 +12756,9 @@
       <c r="AT213" s="1"/>
       <c r="AU213" s="1"/>
       <c r="AV213" s="1"/>
-    </row>
-    <row r="214" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW213" s="1"/>
+    </row>
+    <row r="214" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A214" s="1"/>
       <c r="B214" s="1"/>
       <c r="C214" s="1"/>
@@ -12052,8 +12807,9 @@
       <c r="AT214" s="1"/>
       <c r="AU214" s="1"/>
       <c r="AV214" s="1"/>
-    </row>
-    <row r="215" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW214" s="1"/>
+    </row>
+    <row r="215" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A215" s="1"/>
       <c r="B215" s="1"/>
       <c r="C215" s="1"/>
@@ -12102,8 +12858,9 @@
       <c r="AT215" s="1"/>
       <c r="AU215" s="1"/>
       <c r="AV215" s="1"/>
-    </row>
-    <row r="216" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW215" s="1"/>
+    </row>
+    <row r="216" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A216" s="1"/>
       <c r="B216" s="1"/>
       <c r="C216" s="1"/>
@@ -12152,8 +12909,9 @@
       <c r="AT216" s="1"/>
       <c r="AU216" s="1"/>
       <c r="AV216" s="1"/>
-    </row>
-    <row r="217" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW216" s="1"/>
+    </row>
+    <row r="217" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A217" s="1"/>
       <c r="B217" s="1"/>
       <c r="C217" s="1"/>
@@ -12202,8 +12960,9 @@
       <c r="AT217" s="1"/>
       <c r="AU217" s="1"/>
       <c r="AV217" s="1"/>
-    </row>
-    <row r="218" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW217" s="1"/>
+    </row>
+    <row r="218" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A218" s="1"/>
       <c r="B218" s="1"/>
       <c r="C218" s="1"/>
@@ -12252,8 +13011,9 @@
       <c r="AT218" s="1"/>
       <c r="AU218" s="1"/>
       <c r="AV218" s="1"/>
-    </row>
-    <row r="219" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW218" s="1"/>
+    </row>
+    <row r="219" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A219" s="1"/>
       <c r="B219" s="1"/>
       <c r="C219" s="1"/>
@@ -12302,8 +13062,9 @@
       <c r="AT219" s="1"/>
       <c r="AU219" s="1"/>
       <c r="AV219" s="1"/>
-    </row>
-    <row r="220" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW219" s="1"/>
+    </row>
+    <row r="220" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A220" s="1"/>
       <c r="B220" s="1"/>
       <c r="C220" s="1"/>
@@ -12352,8 +13113,9 @@
       <c r="AT220" s="1"/>
       <c r="AU220" s="1"/>
       <c r="AV220" s="1"/>
-    </row>
-    <row r="221" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW220" s="1"/>
+    </row>
+    <row r="221" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A221" s="1"/>
       <c r="B221" s="1"/>
       <c r="C221" s="1"/>
@@ -12402,8 +13164,9 @@
       <c r="AT221" s="1"/>
       <c r="AU221" s="1"/>
       <c r="AV221" s="1"/>
-    </row>
-    <row r="222" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW221" s="1"/>
+    </row>
+    <row r="222" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A222" s="1"/>
       <c r="B222" s="1"/>
       <c r="C222" s="1"/>
@@ -12452,8 +13215,9 @@
       <c r="AT222" s="1"/>
       <c r="AU222" s="1"/>
       <c r="AV222" s="1"/>
-    </row>
-    <row r="223" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW222" s="1"/>
+    </row>
+    <row r="223" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A223" s="1"/>
       <c r="B223" s="1"/>
       <c r="C223" s="1"/>
@@ -12502,8 +13266,9 @@
       <c r="AT223" s="1"/>
       <c r="AU223" s="1"/>
       <c r="AV223" s="1"/>
-    </row>
-    <row r="224" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW223" s="1"/>
+    </row>
+    <row r="224" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A224" s="1"/>
       <c r="B224" s="1"/>
       <c r="C224" s="1"/>
@@ -12552,8 +13317,9 @@
       <c r="AT224" s="1"/>
       <c r="AU224" s="1"/>
       <c r="AV224" s="1"/>
-    </row>
-    <row r="225" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW224" s="1"/>
+    </row>
+    <row r="225" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A225" s="1"/>
       <c r="B225" s="1"/>
       <c r="C225" s="1"/>
@@ -12602,8 +13368,9 @@
       <c r="AT225" s="1"/>
       <c r="AU225" s="1"/>
       <c r="AV225" s="1"/>
-    </row>
-    <row r="226" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW225" s="1"/>
+    </row>
+    <row r="226" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A226" s="1"/>
       <c r="B226" s="1"/>
       <c r="C226" s="1"/>
@@ -12652,8 +13419,9 @@
       <c r="AT226" s="1"/>
       <c r="AU226" s="1"/>
       <c r="AV226" s="1"/>
-    </row>
-    <row r="227" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW226" s="1"/>
+    </row>
+    <row r="227" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A227" s="1"/>
       <c r="B227" s="1"/>
       <c r="C227" s="1"/>
@@ -12702,8 +13470,9 @@
       <c r="AT227" s="1"/>
       <c r="AU227" s="1"/>
       <c r="AV227" s="1"/>
-    </row>
-    <row r="228" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW227" s="1"/>
+    </row>
+    <row r="228" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A228" s="1"/>
       <c r="B228" s="1"/>
       <c r="C228" s="1"/>
@@ -12752,8 +13521,9 @@
       <c r="AT228" s="1"/>
       <c r="AU228" s="1"/>
       <c r="AV228" s="1"/>
-    </row>
-    <row r="229" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW228" s="1"/>
+    </row>
+    <row r="229" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A229" s="1"/>
       <c r="B229" s="1"/>
       <c r="C229" s="1"/>
@@ -12802,8 +13572,9 @@
       <c r="AT229" s="1"/>
       <c r="AU229" s="1"/>
       <c r="AV229" s="1"/>
-    </row>
-    <row r="230" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW229" s="1"/>
+    </row>
+    <row r="230" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A230" s="1"/>
       <c r="B230" s="1"/>
       <c r="C230" s="1"/>
@@ -12852,8 +13623,9 @@
       <c r="AT230" s="1"/>
       <c r="AU230" s="1"/>
       <c r="AV230" s="1"/>
-    </row>
-    <row r="231" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW230" s="1"/>
+    </row>
+    <row r="231" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A231" s="1"/>
       <c r="B231" s="1"/>
       <c r="C231" s="1"/>
@@ -12902,8 +13674,9 @@
       <c r="AT231" s="1"/>
       <c r="AU231" s="1"/>
       <c r="AV231" s="1"/>
-    </row>
-    <row r="232" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW231" s="1"/>
+    </row>
+    <row r="232" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A232" s="1"/>
       <c r="B232" s="1"/>
       <c r="C232" s="1"/>
@@ -12952,8 +13725,9 @@
       <c r="AT232" s="1"/>
       <c r="AU232" s="1"/>
       <c r="AV232" s="1"/>
-    </row>
-    <row r="233" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW232" s="1"/>
+    </row>
+    <row r="233" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A233" s="1"/>
       <c r="B233" s="1"/>
       <c r="C233" s="1"/>
@@ -13002,8 +13776,9 @@
       <c r="AT233" s="1"/>
       <c r="AU233" s="1"/>
       <c r="AV233" s="1"/>
-    </row>
-    <row r="234" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW233" s="1"/>
+    </row>
+    <row r="234" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A234" s="1"/>
       <c r="B234" s="1"/>
       <c r="C234" s="1"/>
@@ -13052,8 +13827,9 @@
       <c r="AT234" s="1"/>
       <c r="AU234" s="1"/>
       <c r="AV234" s="1"/>
-    </row>
-    <row r="235" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW234" s="1"/>
+    </row>
+    <row r="235" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A235" s="1"/>
       <c r="B235" s="1"/>
       <c r="C235" s="1"/>
@@ -13102,8 +13878,9 @@
       <c r="AT235" s="1"/>
       <c r="AU235" s="1"/>
       <c r="AV235" s="1"/>
-    </row>
-    <row r="236" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW235" s="1"/>
+    </row>
+    <row r="236" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A236" s="1"/>
       <c r="B236" s="1"/>
       <c r="C236" s="1"/>
@@ -13152,8 +13929,9 @@
       <c r="AT236" s="1"/>
       <c r="AU236" s="1"/>
       <c r="AV236" s="1"/>
-    </row>
-    <row r="237" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW236" s="1"/>
+    </row>
+    <row r="237" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A237" s="1"/>
       <c r="B237" s="1"/>
       <c r="C237" s="1"/>
@@ -13202,8 +13980,9 @@
       <c r="AT237" s="1"/>
       <c r="AU237" s="1"/>
       <c r="AV237" s="1"/>
-    </row>
-    <row r="238" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW237" s="1"/>
+    </row>
+    <row r="238" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A238" s="1"/>
       <c r="B238" s="1"/>
       <c r="C238" s="1"/>
@@ -13252,8 +14031,9 @@
       <c r="AT238" s="1"/>
       <c r="AU238" s="1"/>
       <c r="AV238" s="1"/>
-    </row>
-    <row r="239" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW238" s="1"/>
+    </row>
+    <row r="239" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A239" s="1"/>
       <c r="B239" s="1"/>
       <c r="C239" s="1"/>
@@ -13302,8 +14082,9 @@
       <c r="AT239" s="1"/>
       <c r="AU239" s="1"/>
       <c r="AV239" s="1"/>
-    </row>
-    <row r="240" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW239" s="1"/>
+    </row>
+    <row r="240" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A240" s="1"/>
       <c r="B240" s="1"/>
       <c r="C240" s="1"/>
@@ -13352,8 +14133,9 @@
       <c r="AT240" s="1"/>
       <c r="AU240" s="1"/>
       <c r="AV240" s="1"/>
-    </row>
-    <row r="241" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW240" s="1"/>
+    </row>
+    <row r="241" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A241" s="1"/>
       <c r="B241" s="1"/>
       <c r="C241" s="1"/>
@@ -13402,8 +14184,9 @@
       <c r="AT241" s="1"/>
       <c r="AU241" s="1"/>
       <c r="AV241" s="1"/>
-    </row>
-    <row r="242" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW241" s="1"/>
+    </row>
+    <row r="242" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A242" s="1"/>
       <c r="B242" s="1"/>
       <c r="C242" s="1"/>
@@ -13452,8 +14235,9 @@
       <c r="AT242" s="1"/>
       <c r="AU242" s="1"/>
       <c r="AV242" s="1"/>
-    </row>
-    <row r="243" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW242" s="1"/>
+    </row>
+    <row r="243" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A243" s="1"/>
       <c r="B243" s="1"/>
       <c r="C243" s="1"/>
@@ -13502,8 +14286,9 @@
       <c r="AT243" s="1"/>
       <c r="AU243" s="1"/>
       <c r="AV243" s="1"/>
-    </row>
-    <row r="244" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW243" s="1"/>
+    </row>
+    <row r="244" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A244" s="1"/>
       <c r="B244" s="1"/>
       <c r="C244" s="1"/>
@@ -13552,8 +14337,9 @@
       <c r="AT244" s="1"/>
       <c r="AU244" s="1"/>
       <c r="AV244" s="1"/>
-    </row>
-    <row r="245" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW244" s="1"/>
+    </row>
+    <row r="245" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A245" s="1"/>
       <c r="B245" s="1"/>
       <c r="C245" s="1"/>
@@ -13602,8 +14388,9 @@
       <c r="AT245" s="1"/>
       <c r="AU245" s="1"/>
       <c r="AV245" s="1"/>
-    </row>
-    <row r="246" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW245" s="1"/>
+    </row>
+    <row r="246" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A246" s="1"/>
       <c r="B246" s="1"/>
       <c r="C246" s="1"/>
@@ -13652,8 +14439,9 @@
       <c r="AT246" s="1"/>
       <c r="AU246" s="1"/>
       <c r="AV246" s="1"/>
-    </row>
-    <row r="247" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW246" s="1"/>
+    </row>
+    <row r="247" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A247" s="1"/>
       <c r="B247" s="1"/>
       <c r="C247" s="1"/>
@@ -13702,8 +14490,9 @@
       <c r="AT247" s="1"/>
       <c r="AU247" s="1"/>
       <c r="AV247" s="1"/>
-    </row>
-    <row r="248" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW247" s="1"/>
+    </row>
+    <row r="248" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A248" s="1"/>
       <c r="B248" s="1"/>
       <c r="C248" s="1"/>
@@ -13752,8 +14541,9 @@
       <c r="AT248" s="1"/>
       <c r="AU248" s="1"/>
       <c r="AV248" s="1"/>
-    </row>
-    <row r="249" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW248" s="1"/>
+    </row>
+    <row r="249" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A249" s="1"/>
       <c r="B249" s="1"/>
       <c r="C249" s="1"/>
@@ -13802,8 +14592,9 @@
       <c r="AT249" s="1"/>
       <c r="AU249" s="1"/>
       <c r="AV249" s="1"/>
-    </row>
-    <row r="250" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW249" s="1"/>
+    </row>
+    <row r="250" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A250" s="1"/>
       <c r="B250" s="1"/>
       <c r="C250" s="1"/>
@@ -13852,8 +14643,9 @@
       <c r="AT250" s="1"/>
       <c r="AU250" s="1"/>
       <c r="AV250" s="1"/>
-    </row>
-    <row r="251" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW250" s="1"/>
+    </row>
+    <row r="251" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A251" s="1"/>
       <c r="B251" s="1"/>
       <c r="C251" s="1"/>
@@ -13902,8 +14694,9 @@
       <c r="AT251" s="1"/>
       <c r="AU251" s="1"/>
       <c r="AV251" s="1"/>
-    </row>
-    <row r="252" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW251" s="1"/>
+    </row>
+    <row r="252" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A252" s="1"/>
       <c r="B252" s="1"/>
       <c r="C252" s="1"/>
@@ -13952,8 +14745,9 @@
       <c r="AT252" s="1"/>
       <c r="AU252" s="1"/>
       <c r="AV252" s="1"/>
-    </row>
-    <row r="253" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW252" s="1"/>
+    </row>
+    <row r="253" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A253" s="1"/>
       <c r="B253" s="1"/>
       <c r="C253" s="1"/>
@@ -14002,8 +14796,9 @@
       <c r="AT253" s="1"/>
       <c r="AU253" s="1"/>
       <c r="AV253" s="1"/>
-    </row>
-    <row r="254" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW253" s="1"/>
+    </row>
+    <row r="254" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A254" s="1"/>
       <c r="B254" s="1"/>
       <c r="C254" s="1"/>
@@ -14052,8 +14847,9 @@
       <c r="AT254" s="1"/>
       <c r="AU254" s="1"/>
       <c r="AV254" s="1"/>
-    </row>
-    <row r="255" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW254" s="1"/>
+    </row>
+    <row r="255" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A255" s="1"/>
       <c r="B255" s="1"/>
       <c r="C255" s="1"/>
@@ -14102,8 +14898,9 @@
       <c r="AT255" s="1"/>
       <c r="AU255" s="1"/>
       <c r="AV255" s="1"/>
-    </row>
-    <row r="256" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW255" s="1"/>
+    </row>
+    <row r="256" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A256" s="1"/>
       <c r="B256" s="1"/>
       <c r="C256" s="1"/>
@@ -14152,8 +14949,9 @@
       <c r="AT256" s="1"/>
       <c r="AU256" s="1"/>
       <c r="AV256" s="1"/>
-    </row>
-    <row r="257" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW256" s="1"/>
+    </row>
+    <row r="257" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A257" s="1"/>
       <c r="B257" s="1"/>
       <c r="C257" s="1"/>
@@ -14202,8 +15000,9 @@
       <c r="AT257" s="1"/>
       <c r="AU257" s="1"/>
       <c r="AV257" s="1"/>
-    </row>
-    <row r="258" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW257" s="1"/>
+    </row>
+    <row r="258" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A258" s="1"/>
       <c r="B258" s="1"/>
       <c r="C258" s="1"/>
@@ -14252,8 +15051,9 @@
       <c r="AT258" s="1"/>
       <c r="AU258" s="1"/>
       <c r="AV258" s="1"/>
-    </row>
-    <row r="259" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW258" s="1"/>
+    </row>
+    <row r="259" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A259" s="1"/>
       <c r="B259" s="1"/>
       <c r="C259" s="1"/>
@@ -14302,8 +15102,9 @@
       <c r="AT259" s="1"/>
       <c r="AU259" s="1"/>
       <c r="AV259" s="1"/>
-    </row>
-    <row r="260" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW259" s="1"/>
+    </row>
+    <row r="260" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A260" s="1"/>
       <c r="B260" s="1"/>
       <c r="C260" s="1"/>
@@ -14352,8 +15153,9 @@
       <c r="AT260" s="1"/>
       <c r="AU260" s="1"/>
       <c r="AV260" s="1"/>
-    </row>
-    <row r="261" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW260" s="1"/>
+    </row>
+    <row r="261" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A261" s="1"/>
       <c r="B261" s="1"/>
       <c r="C261" s="1"/>
@@ -14402,8 +15204,9 @@
       <c r="AT261" s="1"/>
       <c r="AU261" s="1"/>
       <c r="AV261" s="1"/>
-    </row>
-    <row r="262" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW261" s="1"/>
+    </row>
+    <row r="262" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A262" s="1"/>
       <c r="B262" s="1"/>
       <c r="C262" s="1"/>
@@ -14452,8 +15255,9 @@
       <c r="AT262" s="1"/>
       <c r="AU262" s="1"/>
       <c r="AV262" s="1"/>
-    </row>
-    <row r="263" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW262" s="1"/>
+    </row>
+    <row r="263" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A263" s="1"/>
       <c r="B263" s="1"/>
       <c r="C263" s="1"/>
@@ -14502,8 +15306,9 @@
       <c r="AT263" s="1"/>
       <c r="AU263" s="1"/>
       <c r="AV263" s="1"/>
-    </row>
-    <row r="264" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW263" s="1"/>
+    </row>
+    <row r="264" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A264" s="1"/>
       <c r="B264" s="1"/>
       <c r="C264" s="1"/>
@@ -14552,8 +15357,9 @@
       <c r="AT264" s="1"/>
       <c r="AU264" s="1"/>
       <c r="AV264" s="1"/>
-    </row>
-    <row r="265" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW264" s="1"/>
+    </row>
+    <row r="265" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A265" s="1"/>
       <c r="B265" s="1"/>
       <c r="C265" s="1"/>
@@ -14602,8 +15408,9 @@
       <c r="AT265" s="1"/>
       <c r="AU265" s="1"/>
       <c r="AV265" s="1"/>
-    </row>
-    <row r="266" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW265" s="1"/>
+    </row>
+    <row r="266" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A266" s="1"/>
       <c r="B266" s="1"/>
       <c r="C266" s="1"/>
@@ -14652,8 +15459,9 @@
       <c r="AT266" s="1"/>
       <c r="AU266" s="1"/>
       <c r="AV266" s="1"/>
-    </row>
-    <row r="267" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW266" s="1"/>
+    </row>
+    <row r="267" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A267" s="1"/>
       <c r="B267" s="1"/>
       <c r="C267" s="1"/>
@@ -14702,8 +15510,9 @@
       <c r="AT267" s="1"/>
       <c r="AU267" s="1"/>
       <c r="AV267" s="1"/>
-    </row>
-    <row r="268" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW267" s="1"/>
+    </row>
+    <row r="268" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A268" s="1"/>
       <c r="B268" s="1"/>
       <c r="C268" s="1"/>
@@ -14752,8 +15561,9 @@
       <c r="AT268" s="1"/>
       <c r="AU268" s="1"/>
       <c r="AV268" s="1"/>
-    </row>
-    <row r="269" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW268" s="1"/>
+    </row>
+    <row r="269" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A269" s="1"/>
       <c r="B269" s="1"/>
       <c r="C269" s="1"/>
@@ -14802,8 +15612,9 @@
       <c r="AT269" s="1"/>
       <c r="AU269" s="1"/>
       <c r="AV269" s="1"/>
-    </row>
-    <row r="270" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW269" s="1"/>
+    </row>
+    <row r="270" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A270" s="1"/>
       <c r="B270" s="1"/>
       <c r="C270" s="1"/>
@@ -14852,8 +15663,9 @@
       <c r="AT270" s="1"/>
       <c r="AU270" s="1"/>
       <c r="AV270" s="1"/>
-    </row>
-    <row r="271" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW270" s="1"/>
+    </row>
+    <row r="271" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A271" s="1"/>
       <c r="B271" s="1"/>
       <c r="C271" s="1"/>
@@ -14902,8 +15714,9 @@
       <c r="AT271" s="1"/>
       <c r="AU271" s="1"/>
       <c r="AV271" s="1"/>
-    </row>
-    <row r="272" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW271" s="1"/>
+    </row>
+    <row r="272" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A272" s="1"/>
       <c r="B272" s="1"/>
       <c r="C272" s="1"/>
@@ -14952,8 +15765,9 @@
       <c r="AT272" s="1"/>
       <c r="AU272" s="1"/>
       <c r="AV272" s="1"/>
-    </row>
-    <row r="273" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW272" s="1"/>
+    </row>
+    <row r="273" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A273" s="1"/>
       <c r="B273" s="1"/>
       <c r="C273" s="1"/>
@@ -15002,8 +15816,9 @@
       <c r="AT273" s="1"/>
       <c r="AU273" s="1"/>
       <c r="AV273" s="1"/>
-    </row>
-    <row r="274" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW273" s="1"/>
+    </row>
+    <row r="274" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A274" s="1"/>
       <c r="B274" s="1"/>
       <c r="C274" s="1"/>
@@ -15052,8 +15867,9 @@
       <c r="AT274" s="1"/>
       <c r="AU274" s="1"/>
       <c r="AV274" s="1"/>
-    </row>
-    <row r="275" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW274" s="1"/>
+    </row>
+    <row r="275" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A275" s="1"/>
       <c r="B275" s="1"/>
       <c r="C275" s="1"/>
@@ -15102,8 +15918,9 @@
       <c r="AT275" s="1"/>
       <c r="AU275" s="1"/>
       <c r="AV275" s="1"/>
-    </row>
-    <row r="276" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW275" s="1"/>
+    </row>
+    <row r="276" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A276" s="1"/>
       <c r="B276" s="1"/>
       <c r="C276" s="1"/>
@@ -15152,8 +15969,9 @@
       <c r="AT276" s="1"/>
       <c r="AU276" s="1"/>
       <c r="AV276" s="1"/>
-    </row>
-    <row r="277" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW276" s="1"/>
+    </row>
+    <row r="277" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A277" s="1"/>
       <c r="B277" s="1"/>
       <c r="C277" s="1"/>
@@ -15202,8 +16020,9 @@
       <c r="AT277" s="1"/>
       <c r="AU277" s="1"/>
       <c r="AV277" s="1"/>
-    </row>
-    <row r="278" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW277" s="1"/>
+    </row>
+    <row r="278" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A278" s="1"/>
       <c r="B278" s="1"/>
       <c r="C278" s="1"/>
@@ -15252,8 +16071,9 @@
       <c r="AT278" s="1"/>
       <c r="AU278" s="1"/>
       <c r="AV278" s="1"/>
-    </row>
-    <row r="279" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW278" s="1"/>
+    </row>
+    <row r="279" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A279" s="1"/>
       <c r="B279" s="1"/>
       <c r="C279" s="1"/>
@@ -15302,8 +16122,9 @@
       <c r="AT279" s="1"/>
       <c r="AU279" s="1"/>
       <c r="AV279" s="1"/>
-    </row>
-    <row r="280" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW279" s="1"/>
+    </row>
+    <row r="280" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A280" s="1"/>
       <c r="B280" s="1"/>
       <c r="C280" s="1"/>
@@ -15352,8 +16173,9 @@
       <c r="AT280" s="1"/>
       <c r="AU280" s="1"/>
       <c r="AV280" s="1"/>
-    </row>
-    <row r="281" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW280" s="1"/>
+    </row>
+    <row r="281" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A281" s="1"/>
       <c r="B281" s="1"/>
       <c r="C281" s="1"/>
@@ -15402,8 +16224,9 @@
       <c r="AT281" s="1"/>
       <c r="AU281" s="1"/>
       <c r="AV281" s="1"/>
-    </row>
-    <row r="282" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW281" s="1"/>
+    </row>
+    <row r="282" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A282" s="1"/>
       <c r="B282" s="1"/>
       <c r="C282" s="1"/>
@@ -15452,8 +16275,9 @@
       <c r="AT282" s="1"/>
       <c r="AU282" s="1"/>
       <c r="AV282" s="1"/>
-    </row>
-    <row r="283" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW282" s="1"/>
+    </row>
+    <row r="283" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A283" s="1"/>
       <c r="B283" s="1"/>
       <c r="C283" s="1"/>
@@ -15502,8 +16326,9 @@
       <c r="AT283" s="1"/>
       <c r="AU283" s="1"/>
       <c r="AV283" s="1"/>
-    </row>
-    <row r="284" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW283" s="1"/>
+    </row>
+    <row r="284" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A284" s="1"/>
       <c r="B284" s="1"/>
       <c r="C284" s="1"/>
@@ -15552,8 +16377,9 @@
       <c r="AT284" s="1"/>
       <c r="AU284" s="1"/>
       <c r="AV284" s="1"/>
-    </row>
-    <row r="285" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW284" s="1"/>
+    </row>
+    <row r="285" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A285" s="1"/>
       <c r="B285" s="1"/>
       <c r="C285" s="1"/>
@@ -15602,8 +16428,9 @@
       <c r="AT285" s="1"/>
       <c r="AU285" s="1"/>
       <c r="AV285" s="1"/>
-    </row>
-    <row r="286" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW285" s="1"/>
+    </row>
+    <row r="286" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A286" s="1"/>
       <c r="B286" s="1"/>
       <c r="C286" s="1"/>
@@ -15652,8 +16479,9 @@
       <c r="AT286" s="1"/>
       <c r="AU286" s="1"/>
       <c r="AV286" s="1"/>
-    </row>
-    <row r="287" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW286" s="1"/>
+    </row>
+    <row r="287" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A287" s="1"/>
       <c r="B287" s="1"/>
       <c r="C287" s="1"/>
@@ -15702,8 +16530,9 @@
       <c r="AT287" s="1"/>
       <c r="AU287" s="1"/>
       <c r="AV287" s="1"/>
-    </row>
-    <row r="288" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW287" s="1"/>
+    </row>
+    <row r="288" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A288" s="1"/>
       <c r="B288" s="1"/>
       <c r="C288" s="1"/>
@@ -15752,8 +16581,9 @@
       <c r="AT288" s="1"/>
       <c r="AU288" s="1"/>
       <c r="AV288" s="1"/>
-    </row>
-    <row r="289" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW288" s="1"/>
+    </row>
+    <row r="289" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A289" s="1"/>
       <c r="B289" s="1"/>
       <c r="C289" s="1"/>
@@ -15802,8 +16632,9 @@
       <c r="AT289" s="1"/>
       <c r="AU289" s="1"/>
       <c r="AV289" s="1"/>
-    </row>
-    <row r="290" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW289" s="1"/>
+    </row>
+    <row r="290" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A290" s="1"/>
       <c r="B290" s="1"/>
       <c r="C290" s="1"/>
@@ -15852,8 +16683,9 @@
       <c r="AT290" s="1"/>
       <c r="AU290" s="1"/>
       <c r="AV290" s="1"/>
-    </row>
-    <row r="291" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW290" s="1"/>
+    </row>
+    <row r="291" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A291" s="1"/>
       <c r="B291" s="1"/>
       <c r="C291" s="1"/>
@@ -15902,8 +16734,9 @@
       <c r="AT291" s="1"/>
       <c r="AU291" s="1"/>
       <c r="AV291" s="1"/>
-    </row>
-    <row r="292" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW291" s="1"/>
+    </row>
+    <row r="292" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A292" s="1"/>
       <c r="B292" s="1"/>
       <c r="C292" s="1"/>
@@ -15952,8 +16785,9 @@
       <c r="AT292" s="1"/>
       <c r="AU292" s="1"/>
       <c r="AV292" s="1"/>
-    </row>
-    <row r="293" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW292" s="1"/>
+    </row>
+    <row r="293" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A293" s="1"/>
       <c r="B293" s="1"/>
       <c r="C293" s="1"/>
@@ -16002,8 +16836,9 @@
       <c r="AT293" s="1"/>
       <c r="AU293" s="1"/>
       <c r="AV293" s="1"/>
-    </row>
-    <row r="294" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW293" s="1"/>
+    </row>
+    <row r="294" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A294" s="1"/>
       <c r="B294" s="1"/>
       <c r="C294" s="1"/>
@@ -16052,8 +16887,9 @@
       <c r="AT294" s="1"/>
       <c r="AU294" s="1"/>
       <c r="AV294" s="1"/>
-    </row>
-    <row r="295" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW294" s="1"/>
+    </row>
+    <row r="295" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A295" s="1"/>
       <c r="B295" s="1"/>
       <c r="C295" s="1"/>
@@ -16102,8 +16938,9 @@
       <c r="AT295" s="1"/>
       <c r="AU295" s="1"/>
       <c r="AV295" s="1"/>
-    </row>
-    <row r="296" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW295" s="1"/>
+    </row>
+    <row r="296" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A296" s="1"/>
       <c r="B296" s="1"/>
       <c r="C296" s="1"/>
@@ -16152,8 +16989,9 @@
       <c r="AT296" s="1"/>
       <c r="AU296" s="1"/>
       <c r="AV296" s="1"/>
-    </row>
-    <row r="297" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW296" s="1"/>
+    </row>
+    <row r="297" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A297" s="1"/>
       <c r="B297" s="1"/>
       <c r="C297" s="1"/>
@@ -16202,8 +17040,9 @@
       <c r="AT297" s="1"/>
       <c r="AU297" s="1"/>
       <c r="AV297" s="1"/>
-    </row>
-    <row r="298" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW297" s="1"/>
+    </row>
+    <row r="298" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A298" s="1"/>
       <c r="B298" s="1"/>
       <c r="C298" s="1"/>
@@ -16252,8 +17091,9 @@
       <c r="AT298" s="1"/>
       <c r="AU298" s="1"/>
       <c r="AV298" s="1"/>
-    </row>
-    <row r="299" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW298" s="1"/>
+    </row>
+    <row r="299" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A299" s="1"/>
       <c r="B299" s="1"/>
       <c r="C299" s="1"/>
@@ -16302,8 +17142,9 @@
       <c r="AT299" s="1"/>
       <c r="AU299" s="1"/>
       <c r="AV299" s="1"/>
-    </row>
-    <row r="300" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW299" s="1"/>
+    </row>
+    <row r="300" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A300" s="1"/>
       <c r="B300" s="1"/>
       <c r="C300" s="1"/>
@@ -16352,8 +17193,9 @@
       <c r="AT300" s="1"/>
       <c r="AU300" s="1"/>
       <c r="AV300" s="1"/>
-    </row>
-    <row r="301" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW300" s="1"/>
+    </row>
+    <row r="301" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A301" s="1"/>
       <c r="B301" s="1"/>
       <c r="C301" s="1"/>
@@ -16402,8 +17244,9 @@
       <c r="AT301" s="1"/>
       <c r="AU301" s="1"/>
       <c r="AV301" s="1"/>
-    </row>
-    <row r="302" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW301" s="1"/>
+    </row>
+    <row r="302" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A302" s="1"/>
       <c r="B302" s="1"/>
       <c r="C302" s="1"/>
@@ -16452,8 +17295,9 @@
       <c r="AT302" s="1"/>
       <c r="AU302" s="1"/>
       <c r="AV302" s="1"/>
-    </row>
-    <row r="303" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW302" s="1"/>
+    </row>
+    <row r="303" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A303" s="1"/>
       <c r="B303" s="1"/>
       <c r="C303" s="1"/>
@@ -16502,8 +17346,9 @@
       <c r="AT303" s="1"/>
       <c r="AU303" s="1"/>
       <c r="AV303" s="1"/>
-    </row>
-    <row r="304" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW303" s="1"/>
+    </row>
+    <row r="304" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A304" s="1"/>
       <c r="B304" s="1"/>
       <c r="C304" s="1"/>
@@ -16552,8 +17397,9 @@
       <c r="AT304" s="1"/>
       <c r="AU304" s="1"/>
       <c r="AV304" s="1"/>
-    </row>
-    <row r="305" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW304" s="1"/>
+    </row>
+    <row r="305" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A305" s="1"/>
       <c r="B305" s="1"/>
       <c r="C305" s="1"/>
@@ -16602,8 +17448,9 @@
       <c r="AT305" s="1"/>
       <c r="AU305" s="1"/>
       <c r="AV305" s="1"/>
-    </row>
-    <row r="306" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW305" s="1"/>
+    </row>
+    <row r="306" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A306" s="1"/>
       <c r="B306" s="1"/>
       <c r="C306" s="1"/>
@@ -16652,8 +17499,9 @@
       <c r="AT306" s="1"/>
       <c r="AU306" s="1"/>
       <c r="AV306" s="1"/>
-    </row>
-    <row r="307" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW306" s="1"/>
+    </row>
+    <row r="307" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A307" s="1"/>
       <c r="B307" s="1"/>
       <c r="C307" s="1"/>
@@ -16702,8 +17550,9 @@
       <c r="AT307" s="1"/>
       <c r="AU307" s="1"/>
       <c r="AV307" s="1"/>
-    </row>
-    <row r="308" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW307" s="1"/>
+    </row>
+    <row r="308" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A308" s="1"/>
       <c r="B308" s="1"/>
       <c r="C308" s="1"/>
@@ -16752,8 +17601,9 @@
       <c r="AT308" s="1"/>
       <c r="AU308" s="1"/>
       <c r="AV308" s="1"/>
-    </row>
-    <row r="309" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW308" s="1"/>
+    </row>
+    <row r="309" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A309" s="1"/>
       <c r="B309" s="1"/>
       <c r="C309" s="1"/>
@@ -16802,8 +17652,9 @@
       <c r="AT309" s="1"/>
       <c r="AU309" s="1"/>
       <c r="AV309" s="1"/>
-    </row>
-    <row r="310" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW309" s="1"/>
+    </row>
+    <row r="310" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A310" s="1"/>
       <c r="B310" s="1"/>
       <c r="C310" s="1"/>
@@ -16852,8 +17703,9 @@
       <c r="AT310" s="1"/>
       <c r="AU310" s="1"/>
       <c r="AV310" s="1"/>
-    </row>
-    <row r="311" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW310" s="1"/>
+    </row>
+    <row r="311" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A311" s="1"/>
       <c r="B311" s="1"/>
       <c r="C311" s="1"/>
@@ -16902,8 +17754,9 @@
       <c r="AT311" s="1"/>
       <c r="AU311" s="1"/>
       <c r="AV311" s="1"/>
-    </row>
-    <row r="312" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW311" s="1"/>
+    </row>
+    <row r="312" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A312" s="1"/>
       <c r="B312" s="1"/>
       <c r="C312" s="1"/>
@@ -16952,8 +17805,9 @@
       <c r="AT312" s="1"/>
       <c r="AU312" s="1"/>
       <c r="AV312" s="1"/>
-    </row>
-    <row r="313" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW312" s="1"/>
+    </row>
+    <row r="313" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A313" s="1"/>
       <c r="B313" s="1"/>
       <c r="C313" s="1"/>
@@ -17002,8 +17856,9 @@
       <c r="AT313" s="1"/>
       <c r="AU313" s="1"/>
       <c r="AV313" s="1"/>
-    </row>
-    <row r="314" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW313" s="1"/>
+    </row>
+    <row r="314" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A314" s="1"/>
       <c r="B314" s="1"/>
       <c r="C314" s="1"/>
@@ -17052,8 +17907,9 @@
       <c r="AT314" s="1"/>
       <c r="AU314" s="1"/>
       <c r="AV314" s="1"/>
-    </row>
-    <row r="315" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW314" s="1"/>
+    </row>
+    <row r="315" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A315" s="1"/>
       <c r="B315" s="1"/>
       <c r="C315" s="1"/>
@@ -17102,8 +17958,9 @@
       <c r="AT315" s="1"/>
       <c r="AU315" s="1"/>
       <c r="AV315" s="1"/>
-    </row>
-    <row r="316" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW315" s="1"/>
+    </row>
+    <row r="316" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A316" s="1"/>
       <c r="B316" s="1"/>
       <c r="C316" s="1"/>
@@ -17152,8 +18009,9 @@
       <c r="AT316" s="1"/>
       <c r="AU316" s="1"/>
       <c r="AV316" s="1"/>
-    </row>
-    <row r="317" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW316" s="1"/>
+    </row>
+    <row r="317" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A317" s="1"/>
       <c r="B317" s="1"/>
       <c r="C317" s="1"/>
@@ -17202,8 +18060,9 @@
       <c r="AT317" s="1"/>
       <c r="AU317" s="1"/>
       <c r="AV317" s="1"/>
-    </row>
-    <row r="318" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW317" s="1"/>
+    </row>
+    <row r="318" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A318" s="1"/>
       <c r="B318" s="1"/>
       <c r="C318" s="1"/>
@@ -17252,8 +18111,9 @@
       <c r="AT318" s="1"/>
       <c r="AU318" s="1"/>
       <c r="AV318" s="1"/>
-    </row>
-    <row r="319" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW318" s="1"/>
+    </row>
+    <row r="319" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A319" s="1"/>
       <c r="B319" s="1"/>
       <c r="C319" s="1"/>
@@ -17302,8 +18162,9 @@
       <c r="AT319" s="1"/>
       <c r="AU319" s="1"/>
       <c r="AV319" s="1"/>
-    </row>
-    <row r="320" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW319" s="1"/>
+    </row>
+    <row r="320" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A320" s="1"/>
       <c r="B320" s="1"/>
       <c r="C320" s="1"/>
@@ -17352,8 +18213,9 @@
       <c r="AT320" s="1"/>
       <c r="AU320" s="1"/>
       <c r="AV320" s="1"/>
-    </row>
-    <row r="321" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW320" s="1"/>
+    </row>
+    <row r="321" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A321" s="1"/>
       <c r="B321" s="1"/>
       <c r="C321" s="1"/>
@@ -17402,8 +18264,9 @@
       <c r="AT321" s="1"/>
       <c r="AU321" s="1"/>
       <c r="AV321" s="1"/>
-    </row>
-    <row r="322" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW321" s="1"/>
+    </row>
+    <row r="322" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A322" s="1"/>
       <c r="B322" s="1"/>
       <c r="C322" s="1"/>
@@ -17452,8 +18315,9 @@
       <c r="AT322" s="1"/>
       <c r="AU322" s="1"/>
       <c r="AV322" s="1"/>
-    </row>
-    <row r="323" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW322" s="1"/>
+    </row>
+    <row r="323" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A323" s="1"/>
       <c r="B323" s="1"/>
       <c r="C323" s="1"/>
@@ -17502,8 +18366,9 @@
       <c r="AT323" s="1"/>
       <c r="AU323" s="1"/>
       <c r="AV323" s="1"/>
-    </row>
-    <row r="324" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW323" s="1"/>
+    </row>
+    <row r="324" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A324" s="1"/>
       <c r="B324" s="1"/>
       <c r="C324" s="1"/>
@@ -17552,8 +18417,9 @@
       <c r="AT324" s="1"/>
       <c r="AU324" s="1"/>
       <c r="AV324" s="1"/>
-    </row>
-    <row r="325" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW324" s="1"/>
+    </row>
+    <row r="325" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A325" s="1"/>
       <c r="B325" s="1"/>
       <c r="C325" s="1"/>
@@ -17602,8 +18468,9 @@
       <c r="AT325" s="1"/>
       <c r="AU325" s="1"/>
       <c r="AV325" s="1"/>
-    </row>
-    <row r="326" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW325" s="1"/>
+    </row>
+    <row r="326" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A326" s="1"/>
       <c r="B326" s="1"/>
       <c r="C326" s="1"/>
@@ -17652,8 +18519,9 @@
       <c r="AT326" s="1"/>
       <c r="AU326" s="1"/>
       <c r="AV326" s="1"/>
-    </row>
-    <row r="327" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW326" s="1"/>
+    </row>
+    <row r="327" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A327" s="1"/>
       <c r="B327" s="1"/>
       <c r="C327" s="1"/>
@@ -17702,8 +18570,9 @@
       <c r="AT327" s="1"/>
       <c r="AU327" s="1"/>
       <c r="AV327" s="1"/>
-    </row>
-    <row r="328" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW327" s="1"/>
+    </row>
+    <row r="328" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A328" s="1"/>
       <c r="B328" s="1"/>
       <c r="C328" s="1"/>
@@ -17752,8 +18621,9 @@
       <c r="AT328" s="1"/>
       <c r="AU328" s="1"/>
       <c r="AV328" s="1"/>
-    </row>
-    <row r="329" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW328" s="1"/>
+    </row>
+    <row r="329" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A329" s="1"/>
       <c r="B329" s="1"/>
       <c r="C329" s="1"/>
@@ -17802,8 +18672,9 @@
       <c r="AT329" s="1"/>
       <c r="AU329" s="1"/>
       <c r="AV329" s="1"/>
-    </row>
-    <row r="330" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW329" s="1"/>
+    </row>
+    <row r="330" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A330" s="1"/>
       <c r="B330" s="1"/>
       <c r="C330" s="1"/>
@@ -17852,8 +18723,9 @@
       <c r="AT330" s="1"/>
       <c r="AU330" s="1"/>
       <c r="AV330" s="1"/>
-    </row>
-    <row r="331" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW330" s="1"/>
+    </row>
+    <row r="331" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A331" s="1"/>
       <c r="B331" s="1"/>
       <c r="C331" s="1"/>
@@ -17902,8 +18774,9 @@
       <c r="AT331" s="1"/>
       <c r="AU331" s="1"/>
       <c r="AV331" s="1"/>
-    </row>
-    <row r="332" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW331" s="1"/>
+    </row>
+    <row r="332" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A332" s="1"/>
       <c r="B332" s="1"/>
       <c r="C332" s="1"/>
@@ -17952,8 +18825,9 @@
       <c r="AT332" s="1"/>
       <c r="AU332" s="1"/>
       <c r="AV332" s="1"/>
-    </row>
-    <row r="333" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW332" s="1"/>
+    </row>
+    <row r="333" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A333" s="1"/>
       <c r="B333" s="1"/>
       <c r="C333" s="1"/>
@@ -18002,8 +18876,9 @@
       <c r="AT333" s="1"/>
       <c r="AU333" s="1"/>
       <c r="AV333" s="1"/>
-    </row>
-    <row r="334" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW333" s="1"/>
+    </row>
+    <row r="334" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A334" s="1"/>
       <c r="B334" s="1"/>
       <c r="C334" s="1"/>
@@ -18052,8 +18927,9 @@
       <c r="AT334" s="1"/>
       <c r="AU334" s="1"/>
       <c r="AV334" s="1"/>
-    </row>
-    <row r="335" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW334" s="1"/>
+    </row>
+    <row r="335" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A335" s="1"/>
       <c r="B335" s="1"/>
       <c r="C335" s="1"/>
@@ -18102,8 +18978,9 @@
       <c r="AT335" s="1"/>
       <c r="AU335" s="1"/>
       <c r="AV335" s="1"/>
-    </row>
-    <row r="336" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW335" s="1"/>
+    </row>
+    <row r="336" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A336" s="1"/>
       <c r="B336" s="1"/>
       <c r="C336" s="1"/>
@@ -18152,8 +19029,9 @@
       <c r="AT336" s="1"/>
       <c r="AU336" s="1"/>
       <c r="AV336" s="1"/>
-    </row>
-    <row r="337" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW336" s="1"/>
+    </row>
+    <row r="337" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A337" s="1"/>
       <c r="B337" s="1"/>
       <c r="C337" s="1"/>
@@ -18202,8 +19080,9 @@
       <c r="AT337" s="1"/>
       <c r="AU337" s="1"/>
       <c r="AV337" s="1"/>
-    </row>
-    <row r="338" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW337" s="1"/>
+    </row>
+    <row r="338" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A338" s="1"/>
       <c r="B338" s="1"/>
       <c r="C338" s="1"/>
@@ -18252,8 +19131,9 @@
       <c r="AT338" s="1"/>
       <c r="AU338" s="1"/>
       <c r="AV338" s="1"/>
-    </row>
-    <row r="339" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW338" s="1"/>
+    </row>
+    <row r="339" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A339" s="1"/>
       <c r="B339" s="1"/>
       <c r="C339" s="1"/>
@@ -18302,8 +19182,9 @@
       <c r="AT339" s="1"/>
       <c r="AU339" s="1"/>
       <c r="AV339" s="1"/>
-    </row>
-    <row r="340" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW339" s="1"/>
+    </row>
+    <row r="340" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A340" s="1"/>
       <c r="B340" s="1"/>
       <c r="C340" s="1"/>
@@ -18352,8 +19233,9 @@
       <c r="AT340" s="1"/>
       <c r="AU340" s="1"/>
       <c r="AV340" s="1"/>
-    </row>
-    <row r="341" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW340" s="1"/>
+    </row>
+    <row r="341" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A341" s="1"/>
       <c r="B341" s="1"/>
       <c r="C341" s="1"/>
@@ -18402,8 +19284,9 @@
       <c r="AT341" s="1"/>
       <c r="AU341" s="1"/>
       <c r="AV341" s="1"/>
-    </row>
-    <row r="342" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW341" s="1"/>
+    </row>
+    <row r="342" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A342" s="1"/>
       <c r="B342" s="1"/>
       <c r="C342" s="1"/>
@@ -18452,8 +19335,9 @@
       <c r="AT342" s="1"/>
       <c r="AU342" s="1"/>
       <c r="AV342" s="1"/>
-    </row>
-    <row r="343" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW342" s="1"/>
+    </row>
+    <row r="343" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A343" s="1"/>
       <c r="B343" s="1"/>
       <c r="C343" s="1"/>
@@ -18502,8 +19386,9 @@
       <c r="AT343" s="1"/>
       <c r="AU343" s="1"/>
       <c r="AV343" s="1"/>
-    </row>
-    <row r="344" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW343" s="1"/>
+    </row>
+    <row r="344" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A344" s="1"/>
       <c r="B344" s="1"/>
       <c r="C344" s="1"/>
@@ -18552,8 +19437,9 @@
       <c r="AT344" s="1"/>
       <c r="AU344" s="1"/>
       <c r="AV344" s="1"/>
-    </row>
-    <row r="345" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW344" s="1"/>
+    </row>
+    <row r="345" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A345" s="1"/>
       <c r="B345" s="1"/>
       <c r="C345" s="1"/>
@@ -18602,8 +19488,9 @@
       <c r="AT345" s="1"/>
       <c r="AU345" s="1"/>
       <c r="AV345" s="1"/>
-    </row>
-    <row r="346" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW345" s="1"/>
+    </row>
+    <row r="346" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A346" s="1"/>
       <c r="B346" s="1"/>
       <c r="C346" s="1"/>
@@ -18652,8 +19539,9 @@
       <c r="AT346" s="1"/>
       <c r="AU346" s="1"/>
       <c r="AV346" s="1"/>
-    </row>
-    <row r="347" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW346" s="1"/>
+    </row>
+    <row r="347" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A347" s="1"/>
       <c r="B347" s="1"/>
       <c r="C347" s="1"/>
@@ -18702,8 +19590,9 @@
       <c r="AT347" s="1"/>
       <c r="AU347" s="1"/>
       <c r="AV347" s="1"/>
-    </row>
-    <row r="348" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW347" s="1"/>
+    </row>
+    <row r="348" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A348" s="1"/>
       <c r="B348" s="1"/>
       <c r="C348" s="1"/>
@@ -18752,8 +19641,9 @@
       <c r="AT348" s="1"/>
       <c r="AU348" s="1"/>
       <c r="AV348" s="1"/>
-    </row>
-    <row r="349" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW348" s="1"/>
+    </row>
+    <row r="349" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A349" s="1"/>
       <c r="B349" s="1"/>
       <c r="C349" s="1"/>
@@ -18802,8 +19692,9 @@
       <c r="AT349" s="1"/>
       <c r="AU349" s="1"/>
       <c r="AV349" s="1"/>
-    </row>
-    <row r="350" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW349" s="1"/>
+    </row>
+    <row r="350" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A350" s="1"/>
       <c r="B350" s="1"/>
       <c r="C350" s="1"/>
@@ -18852,8 +19743,9 @@
       <c r="AT350" s="1"/>
       <c r="AU350" s="1"/>
       <c r="AV350" s="1"/>
-    </row>
-    <row r="351" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW350" s="1"/>
+    </row>
+    <row r="351" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A351" s="1"/>
       <c r="B351" s="1"/>
       <c r="C351" s="1"/>
@@ -18902,8 +19794,9 @@
       <c r="AT351" s="1"/>
       <c r="AU351" s="1"/>
       <c r="AV351" s="1"/>
-    </row>
-    <row r="352" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW351" s="1"/>
+    </row>
+    <row r="352" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A352" s="1"/>
       <c r="B352" s="1"/>
       <c r="C352" s="1"/>
@@ -18952,8 +19845,9 @@
       <c r="AT352" s="1"/>
       <c r="AU352" s="1"/>
       <c r="AV352" s="1"/>
-    </row>
-    <row r="353" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW352" s="1"/>
+    </row>
+    <row r="353" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A353" s="1"/>
       <c r="B353" s="1"/>
       <c r="C353" s="1"/>
@@ -19002,8 +19896,9 @@
       <c r="AT353" s="1"/>
       <c r="AU353" s="1"/>
       <c r="AV353" s="1"/>
-    </row>
-    <row r="354" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW353" s="1"/>
+    </row>
+    <row r="354" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A354" s="1"/>
       <c r="B354" s="1"/>
       <c r="C354" s="1"/>
@@ -19052,8 +19947,9 @@
       <c r="AT354" s="1"/>
       <c r="AU354" s="1"/>
       <c r="AV354" s="1"/>
-    </row>
-    <row r="355" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW354" s="1"/>
+    </row>
+    <row r="355" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A355" s="1"/>
       <c r="B355" s="1"/>
       <c r="C355" s="1"/>
@@ -19102,8 +19998,9 @@
       <c r="AT355" s="1"/>
       <c r="AU355" s="1"/>
       <c r="AV355" s="1"/>
-    </row>
-    <row r="356" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW355" s="1"/>
+    </row>
+    <row r="356" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A356" s="1"/>
       <c r="B356" s="1"/>
       <c r="C356" s="1"/>
@@ -19152,8 +20049,9 @@
       <c r="AT356" s="1"/>
       <c r="AU356" s="1"/>
       <c r="AV356" s="1"/>
-    </row>
-    <row r="357" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW356" s="1"/>
+    </row>
+    <row r="357" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A357" s="1"/>
       <c r="B357" s="1"/>
       <c r="C357" s="1"/>
@@ -19202,8 +20100,9 @@
       <c r="AT357" s="1"/>
       <c r="AU357" s="1"/>
       <c r="AV357" s="1"/>
-    </row>
-    <row r="358" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW357" s="1"/>
+    </row>
+    <row r="358" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A358" s="1"/>
       <c r="B358" s="1"/>
       <c r="C358" s="1"/>
@@ -19252,8 +20151,9 @@
       <c r="AT358" s="1"/>
       <c r="AU358" s="1"/>
       <c r="AV358" s="1"/>
-    </row>
-    <row r="359" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW358" s="1"/>
+    </row>
+    <row r="359" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A359" s="1"/>
       <c r="B359" s="1"/>
       <c r="C359" s="1"/>
@@ -19302,8 +20202,9 @@
       <c r="AT359" s="1"/>
       <c r="AU359" s="1"/>
       <c r="AV359" s="1"/>
-    </row>
-    <row r="360" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW359" s="1"/>
+    </row>
+    <row r="360" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A360" s="1"/>
       <c r="B360" s="1"/>
       <c r="C360" s="1"/>
@@ -19352,8 +20253,9 @@
       <c r="AT360" s="1"/>
       <c r="AU360" s="1"/>
       <c r="AV360" s="1"/>
-    </row>
-    <row r="361" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW360" s="1"/>
+    </row>
+    <row r="361" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A361" s="1"/>
       <c r="B361" s="1"/>
       <c r="C361" s="1"/>
@@ -19402,8 +20304,9 @@
       <c r="AT361" s="1"/>
       <c r="AU361" s="1"/>
       <c r="AV361" s="1"/>
-    </row>
-    <row r="362" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW361" s="1"/>
+    </row>
+    <row r="362" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A362" s="1"/>
       <c r="B362" s="1"/>
       <c r="C362" s="1"/>
@@ -19452,8 +20355,9 @@
       <c r="AT362" s="1"/>
       <c r="AU362" s="1"/>
       <c r="AV362" s="1"/>
-    </row>
-    <row r="363" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW362" s="1"/>
+    </row>
+    <row r="363" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A363" s="1"/>
       <c r="B363" s="1"/>
       <c r="C363" s="1"/>
@@ -19502,8 +20406,9 @@
       <c r="AT363" s="1"/>
       <c r="AU363" s="1"/>
       <c r="AV363" s="1"/>
-    </row>
-    <row r="364" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW363" s="1"/>
+    </row>
+    <row r="364" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A364" s="1"/>
       <c r="B364" s="1"/>
       <c r="C364" s="1"/>
@@ -19552,8 +20457,9 @@
       <c r="AT364" s="1"/>
       <c r="AU364" s="1"/>
       <c r="AV364" s="1"/>
-    </row>
-    <row r="365" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW364" s="1"/>
+    </row>
+    <row r="365" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A365" s="1"/>
       <c r="B365" s="1"/>
       <c r="C365" s="1"/>
@@ -19602,8 +20508,9 @@
       <c r="AT365" s="1"/>
       <c r="AU365" s="1"/>
       <c r="AV365" s="1"/>
-    </row>
-    <row r="366" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW365" s="1"/>
+    </row>
+    <row r="366" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A366" s="1"/>
       <c r="B366" s="1"/>
       <c r="C366" s="1"/>
@@ -19652,8 +20559,9 @@
       <c r="AT366" s="1"/>
       <c r="AU366" s="1"/>
       <c r="AV366" s="1"/>
-    </row>
-    <row r="367" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW366" s="1"/>
+    </row>
+    <row r="367" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A367" s="1"/>
       <c r="B367" s="1"/>
       <c r="C367" s="1"/>
@@ -19702,8 +20610,9 @@
       <c r="AT367" s="1"/>
       <c r="AU367" s="1"/>
       <c r="AV367" s="1"/>
-    </row>
-    <row r="368" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW367" s="1"/>
+    </row>
+    <row r="368" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A368" s="1"/>
       <c r="B368" s="1"/>
       <c r="C368" s="1"/>
@@ -19752,8 +20661,9 @@
       <c r="AT368" s="1"/>
       <c r="AU368" s="1"/>
       <c r="AV368" s="1"/>
-    </row>
-    <row r="369" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW368" s="1"/>
+    </row>
+    <row r="369" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A369" s="1"/>
       <c r="B369" s="1"/>
       <c r="C369" s="1"/>
@@ -19802,8 +20712,9 @@
       <c r="AT369" s="1"/>
       <c r="AU369" s="1"/>
       <c r="AV369" s="1"/>
-    </row>
-    <row r="370" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW369" s="1"/>
+    </row>
+    <row r="370" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A370" s="1"/>
       <c r="B370" s="1"/>
       <c r="C370" s="1"/>
@@ -19852,8 +20763,9 @@
       <c r="AT370" s="1"/>
       <c r="AU370" s="1"/>
       <c r="AV370" s="1"/>
-    </row>
-    <row r="371" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW370" s="1"/>
+    </row>
+    <row r="371" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A371" s="1"/>
       <c r="B371" s="1"/>
       <c r="C371" s="1"/>
@@ -19902,8 +20814,9 @@
       <c r="AT371" s="1"/>
       <c r="AU371" s="1"/>
       <c r="AV371" s="1"/>
-    </row>
-    <row r="372" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW371" s="1"/>
+    </row>
+    <row r="372" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A372" s="1"/>
       <c r="B372" s="1"/>
       <c r="C372" s="1"/>
@@ -19952,8 +20865,9 @@
       <c r="AT372" s="1"/>
       <c r="AU372" s="1"/>
       <c r="AV372" s="1"/>
-    </row>
-    <row r="373" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW372" s="1"/>
+    </row>
+    <row r="373" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A373" s="1"/>
       <c r="B373" s="1"/>
       <c r="C373" s="1"/>
@@ -20002,8 +20916,9 @@
       <c r="AT373" s="1"/>
       <c r="AU373" s="1"/>
       <c r="AV373" s="1"/>
-    </row>
-    <row r="374" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW373" s="1"/>
+    </row>
+    <row r="374" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A374" s="1"/>
       <c r="B374" s="1"/>
       <c r="C374" s="1"/>
@@ -20052,8 +20967,9 @@
       <c r="AT374" s="1"/>
       <c r="AU374" s="1"/>
       <c r="AV374" s="1"/>
-    </row>
-    <row r="375" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW374" s="1"/>
+    </row>
+    <row r="375" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A375" s="1"/>
       <c r="B375" s="1"/>
       <c r="C375" s="1"/>
@@ -20102,8 +21018,9 @@
       <c r="AT375" s="1"/>
       <c r="AU375" s="1"/>
       <c r="AV375" s="1"/>
-    </row>
-    <row r="376" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW375" s="1"/>
+    </row>
+    <row r="376" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A376" s="1"/>
       <c r="B376" s="1"/>
       <c r="C376" s="1"/>
@@ -20152,8 +21069,9 @@
       <c r="AT376" s="1"/>
       <c r="AU376" s="1"/>
       <c r="AV376" s="1"/>
-    </row>
-    <row r="377" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW376" s="1"/>
+    </row>
+    <row r="377" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A377" s="1"/>
       <c r="B377" s="1"/>
       <c r="C377" s="1"/>
@@ -20202,8 +21120,9 @@
       <c r="AT377" s="1"/>
       <c r="AU377" s="1"/>
       <c r="AV377" s="1"/>
-    </row>
-    <row r="378" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW377" s="1"/>
+    </row>
+    <row r="378" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A378" s="1"/>
       <c r="B378" s="1"/>
       <c r="C378" s="1"/>
@@ -20252,8 +21171,9 @@
       <c r="AT378" s="1"/>
       <c r="AU378" s="1"/>
       <c r="AV378" s="1"/>
-    </row>
-    <row r="379" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW378" s="1"/>
+    </row>
+    <row r="379" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A379" s="1"/>
       <c r="B379" s="1"/>
       <c r="C379" s="1"/>
@@ -20302,8 +21222,9 @@
       <c r="AT379" s="1"/>
       <c r="AU379" s="1"/>
       <c r="AV379" s="1"/>
-    </row>
-    <row r="380" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW379" s="1"/>
+    </row>
+    <row r="380" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A380" s="1"/>
       <c r="B380" s="1"/>
       <c r="C380" s="1"/>
@@ -20352,8 +21273,9 @@
       <c r="AT380" s="1"/>
       <c r="AU380" s="1"/>
       <c r="AV380" s="1"/>
-    </row>
-    <row r="381" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW380" s="1"/>
+    </row>
+    <row r="381" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A381" s="1"/>
       <c r="B381" s="1"/>
       <c r="C381" s="1"/>
@@ -20402,8 +21324,9 @@
       <c r="AT381" s="1"/>
       <c r="AU381" s="1"/>
       <c r="AV381" s="1"/>
-    </row>
-    <row r="382" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW381" s="1"/>
+    </row>
+    <row r="382" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A382" s="1"/>
       <c r="B382" s="1"/>
       <c r="C382" s="1"/>
@@ -20452,8 +21375,9 @@
       <c r="AT382" s="1"/>
       <c r="AU382" s="1"/>
       <c r="AV382" s="1"/>
-    </row>
-    <row r="383" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW382" s="1"/>
+    </row>
+    <row r="383" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A383" s="1"/>
       <c r="B383" s="1"/>
       <c r="C383" s="1"/>
@@ -20502,8 +21426,9 @@
       <c r="AT383" s="1"/>
       <c r="AU383" s="1"/>
       <c r="AV383" s="1"/>
-    </row>
-    <row r="384" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW383" s="1"/>
+    </row>
+    <row r="384" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A384" s="1"/>
       <c r="B384" s="1"/>
       <c r="C384" s="1"/>
@@ -20552,8 +21477,9 @@
       <c r="AT384" s="1"/>
       <c r="AU384" s="1"/>
       <c r="AV384" s="1"/>
-    </row>
-    <row r="385" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW384" s="1"/>
+    </row>
+    <row r="385" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A385" s="1"/>
       <c r="B385" s="1"/>
       <c r="C385" s="1"/>
@@ -20602,8 +21528,9 @@
       <c r="AT385" s="1"/>
       <c r="AU385" s="1"/>
       <c r="AV385" s="1"/>
-    </row>
-    <row r="386" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW385" s="1"/>
+    </row>
+    <row r="386" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A386" s="1"/>
       <c r="B386" s="1"/>
       <c r="C386" s="1"/>
@@ -20652,8 +21579,9 @@
       <c r="AT386" s="1"/>
       <c r="AU386" s="1"/>
       <c r="AV386" s="1"/>
-    </row>
-    <row r="387" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW386" s="1"/>
+    </row>
+    <row r="387" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A387" s="1"/>
       <c r="B387" s="1"/>
       <c r="C387" s="1"/>
@@ -20702,8 +21630,9 @@
       <c r="AT387" s="1"/>
       <c r="AU387" s="1"/>
       <c r="AV387" s="1"/>
-    </row>
-    <row r="388" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW387" s="1"/>
+    </row>
+    <row r="388" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A388" s="1"/>
       <c r="B388" s="1"/>
       <c r="C388" s="1"/>
@@ -20752,8 +21681,9 @@
       <c r="AT388" s="1"/>
       <c r="AU388" s="1"/>
       <c r="AV388" s="1"/>
-    </row>
-    <row r="389" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW388" s="1"/>
+    </row>
+    <row r="389" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A389" s="1"/>
       <c r="B389" s="1"/>
       <c r="C389" s="1"/>
@@ -20802,8 +21732,9 @@
       <c r="AT389" s="1"/>
       <c r="AU389" s="1"/>
       <c r="AV389" s="1"/>
-    </row>
-    <row r="390" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW389" s="1"/>
+    </row>
+    <row r="390" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A390" s="1"/>
       <c r="B390" s="1"/>
       <c r="C390" s="1"/>
@@ -20852,8 +21783,9 @@
       <c r="AT390" s="1"/>
       <c r="AU390" s="1"/>
       <c r="AV390" s="1"/>
-    </row>
-    <row r="391" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW390" s="1"/>
+    </row>
+    <row r="391" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A391" s="1"/>
       <c r="B391" s="1"/>
       <c r="C391" s="1"/>
@@ -20902,8 +21834,9 @@
       <c r="AT391" s="1"/>
       <c r="AU391" s="1"/>
       <c r="AV391" s="1"/>
-    </row>
-    <row r="392" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW391" s="1"/>
+    </row>
+    <row r="392" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A392" s="1"/>
       <c r="B392" s="1"/>
       <c r="C392" s="1"/>
@@ -20952,8 +21885,9 @@
       <c r="AT392" s="1"/>
       <c r="AU392" s="1"/>
       <c r="AV392" s="1"/>
-    </row>
-    <row r="393" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW392" s="1"/>
+    </row>
+    <row r="393" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A393" s="1"/>
       <c r="B393" s="1"/>
       <c r="C393" s="1"/>
@@ -21002,8 +21936,9 @@
       <c r="AT393" s="1"/>
       <c r="AU393" s="1"/>
       <c r="AV393" s="1"/>
-    </row>
-    <row r="394" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW393" s="1"/>
+    </row>
+    <row r="394" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A394" s="1"/>
       <c r="B394" s="1"/>
       <c r="C394" s="1"/>
@@ -21052,8 +21987,9 @@
       <c r="AT394" s="1"/>
       <c r="AU394" s="1"/>
       <c r="AV394" s="1"/>
-    </row>
-    <row r="395" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW394" s="1"/>
+    </row>
+    <row r="395" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A395" s="1"/>
       <c r="B395" s="1"/>
       <c r="C395" s="1"/>
@@ -21102,8 +22038,9 @@
       <c r="AT395" s="1"/>
       <c r="AU395" s="1"/>
       <c r="AV395" s="1"/>
-    </row>
-    <row r="396" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW395" s="1"/>
+    </row>
+    <row r="396" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A396" s="1"/>
       <c r="B396" s="1"/>
       <c r="C396" s="1"/>
@@ -21152,8 +22089,9 @@
       <c r="AT396" s="1"/>
       <c r="AU396" s="1"/>
       <c r="AV396" s="1"/>
-    </row>
-    <row r="397" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW396" s="1"/>
+    </row>
+    <row r="397" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A397" s="1"/>
       <c r="B397" s="1"/>
       <c r="C397" s="1"/>
@@ -21202,8 +22140,9 @@
       <c r="AT397" s="1"/>
       <c r="AU397" s="1"/>
       <c r="AV397" s="1"/>
-    </row>
-    <row r="398" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW397" s="1"/>
+    </row>
+    <row r="398" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A398" s="1"/>
       <c r="B398" s="1"/>
       <c r="C398" s="1"/>
@@ -21252,8 +22191,9 @@
       <c r="AT398" s="1"/>
       <c r="AU398" s="1"/>
       <c r="AV398" s="1"/>
-    </row>
-    <row r="399" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW398" s="1"/>
+    </row>
+    <row r="399" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A399" s="1"/>
       <c r="B399" s="1"/>
       <c r="C399" s="1"/>
@@ -21302,8 +22242,9 @@
       <c r="AT399" s="1"/>
       <c r="AU399" s="1"/>
       <c r="AV399" s="1"/>
-    </row>
-    <row r="400" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW399" s="1"/>
+    </row>
+    <row r="400" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A400" s="1"/>
       <c r="B400" s="1"/>
       <c r="C400" s="1"/>
@@ -21352,8 +22293,9 @@
       <c r="AT400" s="1"/>
       <c r="AU400" s="1"/>
       <c r="AV400" s="1"/>
-    </row>
-    <row r="401" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW400" s="1"/>
+    </row>
+    <row r="401" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A401" s="1"/>
       <c r="B401" s="1"/>
       <c r="C401" s="1"/>
@@ -21402,8 +22344,9 @@
       <c r="AT401" s="1"/>
       <c r="AU401" s="1"/>
       <c r="AV401" s="1"/>
-    </row>
-    <row r="402" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW401" s="1"/>
+    </row>
+    <row r="402" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A402" s="1"/>
       <c r="B402" s="1"/>
       <c r="C402" s="1"/>
@@ -21452,8 +22395,9 @@
       <c r="AT402" s="1"/>
       <c r="AU402" s="1"/>
       <c r="AV402" s="1"/>
-    </row>
-    <row r="403" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW402" s="1"/>
+    </row>
+    <row r="403" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A403" s="1"/>
       <c r="B403" s="1"/>
       <c r="C403" s="1"/>
@@ -21502,8 +22446,9 @@
       <c r="AT403" s="1"/>
       <c r="AU403" s="1"/>
       <c r="AV403" s="1"/>
-    </row>
-    <row r="404" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW403" s="1"/>
+    </row>
+    <row r="404" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A404" s="1"/>
       <c r="B404" s="1"/>
       <c r="C404" s="1"/>
@@ -21552,8 +22497,9 @@
       <c r="AT404" s="1"/>
       <c r="AU404" s="1"/>
       <c r="AV404" s="1"/>
-    </row>
-    <row r="405" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW404" s="1"/>
+    </row>
+    <row r="405" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A405" s="1"/>
       <c r="B405" s="1"/>
       <c r="C405" s="1"/>
@@ -21602,8 +22548,9 @@
       <c r="AT405" s="1"/>
       <c r="AU405" s="1"/>
       <c r="AV405" s="1"/>
-    </row>
-    <row r="406" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW405" s="1"/>
+    </row>
+    <row r="406" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A406" s="1"/>
       <c r="B406" s="1"/>
       <c r="C406" s="1"/>
@@ -21652,8 +22599,9 @@
       <c r="AT406" s="1"/>
       <c r="AU406" s="1"/>
       <c r="AV406" s="1"/>
-    </row>
-    <row r="407" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW406" s="1"/>
+    </row>
+    <row r="407" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A407" s="1"/>
       <c r="B407" s="1"/>
       <c r="C407" s="1"/>
@@ -21702,8 +22650,9 @@
       <c r="AT407" s="1"/>
       <c r="AU407" s="1"/>
       <c r="AV407" s="1"/>
-    </row>
-    <row r="408" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW407" s="1"/>
+    </row>
+    <row r="408" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A408" s="1"/>
       <c r="B408" s="1"/>
       <c r="C408" s="1"/>
@@ -21752,8 +22701,9 @@
       <c r="AT408" s="1"/>
       <c r="AU408" s="1"/>
       <c r="AV408" s="1"/>
-    </row>
-    <row r="409" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW408" s="1"/>
+    </row>
+    <row r="409" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A409" s="1"/>
       <c r="B409" s="1"/>
       <c r="C409" s="1"/>
@@ -21802,8 +22752,9 @@
       <c r="AT409" s="1"/>
       <c r="AU409" s="1"/>
       <c r="AV409" s="1"/>
-    </row>
-    <row r="410" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW409" s="1"/>
+    </row>
+    <row r="410" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A410" s="1"/>
       <c r="B410" s="1"/>
       <c r="C410" s="1"/>
@@ -21852,8 +22803,9 @@
       <c r="AT410" s="1"/>
       <c r="AU410" s="1"/>
       <c r="AV410" s="1"/>
-    </row>
-    <row r="411" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW410" s="1"/>
+    </row>
+    <row r="411" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A411" s="1"/>
       <c r="B411" s="1"/>
       <c r="C411" s="1"/>
@@ -21902,8 +22854,9 @@
       <c r="AT411" s="1"/>
       <c r="AU411" s="1"/>
       <c r="AV411" s="1"/>
-    </row>
-    <row r="412" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW411" s="1"/>
+    </row>
+    <row r="412" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A412" s="1"/>
       <c r="B412" s="1"/>
       <c r="C412" s="1"/>
@@ -21952,8 +22905,9 @@
       <c r="AT412" s="1"/>
       <c r="AU412" s="1"/>
       <c r="AV412" s="1"/>
-    </row>
-    <row r="413" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW412" s="1"/>
+    </row>
+    <row r="413" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A413" s="1"/>
       <c r="B413" s="1"/>
       <c r="C413" s="1"/>
@@ -22002,8 +22956,9 @@
       <c r="AT413" s="1"/>
       <c r="AU413" s="1"/>
       <c r="AV413" s="1"/>
-    </row>
-    <row r="414" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW413" s="1"/>
+    </row>
+    <row r="414" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A414" s="1"/>
       <c r="B414" s="1"/>
       <c r="C414" s="1"/>
@@ -22052,8 +23007,9 @@
       <c r="AT414" s="1"/>
       <c r="AU414" s="1"/>
       <c r="AV414" s="1"/>
-    </row>
-    <row r="415" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW414" s="1"/>
+    </row>
+    <row r="415" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A415" s="1"/>
       <c r="B415" s="1"/>
       <c r="C415" s="1"/>
@@ -22102,8 +23058,9 @@
       <c r="AT415" s="1"/>
       <c r="AU415" s="1"/>
       <c r="AV415" s="1"/>
-    </row>
-    <row r="416" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW415" s="1"/>
+    </row>
+    <row r="416" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A416" s="1"/>
       <c r="B416" s="1"/>
       <c r="C416" s="1"/>
@@ -22152,8 +23109,9 @@
       <c r="AT416" s="1"/>
       <c r="AU416" s="1"/>
       <c r="AV416" s="1"/>
-    </row>
-    <row r="417" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW416" s="1"/>
+    </row>
+    <row r="417" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A417" s="1"/>
       <c r="B417" s="1"/>
       <c r="C417" s="1"/>
@@ -22202,8 +23160,9 @@
       <c r="AT417" s="1"/>
       <c r="AU417" s="1"/>
       <c r="AV417" s="1"/>
-    </row>
-    <row r="418" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW417" s="1"/>
+    </row>
+    <row r="418" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A418" s="1"/>
       <c r="B418" s="1"/>
       <c r="C418" s="1"/>
@@ -22252,8 +23211,9 @@
       <c r="AT418" s="1"/>
       <c r="AU418" s="1"/>
       <c r="AV418" s="1"/>
-    </row>
-    <row r="419" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW418" s="1"/>
+    </row>
+    <row r="419" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A419" s="1"/>
       <c r="B419" s="1"/>
       <c r="C419" s="1"/>
@@ -22302,8 +23262,9 @@
       <c r="AT419" s="1"/>
       <c r="AU419" s="1"/>
       <c r="AV419" s="1"/>
-    </row>
-    <row r="420" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW419" s="1"/>
+    </row>
+    <row r="420" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A420" s="1"/>
       <c r="B420" s="1"/>
       <c r="C420" s="1"/>
@@ -22352,8 +23313,9 @@
       <c r="AT420" s="1"/>
       <c r="AU420" s="1"/>
       <c r="AV420" s="1"/>
-    </row>
-    <row r="421" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW420" s="1"/>
+    </row>
+    <row r="421" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A421" s="1"/>
       <c r="B421" s="1"/>
       <c r="C421" s="1"/>
@@ -22402,8 +23364,9 @@
       <c r="AT421" s="1"/>
       <c r="AU421" s="1"/>
       <c r="AV421" s="1"/>
-    </row>
-    <row r="422" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW421" s="1"/>
+    </row>
+    <row r="422" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A422" s="1"/>
       <c r="B422" s="1"/>
       <c r="C422" s="1"/>
@@ -22452,8 +23415,9 @@
       <c r="AT422" s="1"/>
       <c r="AU422" s="1"/>
       <c r="AV422" s="1"/>
-    </row>
-    <row r="423" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW422" s="1"/>
+    </row>
+    <row r="423" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A423" s="1"/>
       <c r="B423" s="1"/>
       <c r="C423" s="1"/>
@@ -22502,8 +23466,9 @@
       <c r="AT423" s="1"/>
       <c r="AU423" s="1"/>
       <c r="AV423" s="1"/>
-    </row>
-    <row r="424" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW423" s="1"/>
+    </row>
+    <row r="424" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A424" s="1"/>
       <c r="B424" s="1"/>
       <c r="C424" s="1"/>
@@ -22552,8 +23517,9 @@
       <c r="AT424" s="1"/>
       <c r="AU424" s="1"/>
       <c r="AV424" s="1"/>
-    </row>
-    <row r="425" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW424" s="1"/>
+    </row>
+    <row r="425" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A425" s="1"/>
       <c r="B425" s="1"/>
       <c r="C425" s="1"/>
@@ -22602,8 +23568,9 @@
       <c r="AT425" s="1"/>
       <c r="AU425" s="1"/>
       <c r="AV425" s="1"/>
-    </row>
-    <row r="426" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW425" s="1"/>
+    </row>
+    <row r="426" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A426" s="1"/>
       <c r="B426" s="1"/>
       <c r="C426" s="1"/>
@@ -22652,8 +23619,9 @@
       <c r="AT426" s="1"/>
       <c r="AU426" s="1"/>
       <c r="AV426" s="1"/>
-    </row>
-    <row r="427" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW426" s="1"/>
+    </row>
+    <row r="427" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A427" s="1"/>
       <c r="B427" s="1"/>
       <c r="C427" s="1"/>
@@ -22702,8 +23670,9 @@
       <c r="AT427" s="1"/>
       <c r="AU427" s="1"/>
       <c r="AV427" s="1"/>
-    </row>
-    <row r="428" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW427" s="1"/>
+    </row>
+    <row r="428" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A428" s="1"/>
       <c r="B428" s="1"/>
       <c r="C428" s="1"/>
@@ -22752,8 +23721,9 @@
       <c r="AT428" s="1"/>
       <c r="AU428" s="1"/>
       <c r="AV428" s="1"/>
-    </row>
-    <row r="429" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW428" s="1"/>
+    </row>
+    <row r="429" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A429" s="1"/>
       <c r="B429" s="1"/>
       <c r="C429" s="1"/>
@@ -22802,8 +23772,9 @@
       <c r="AT429" s="1"/>
       <c r="AU429" s="1"/>
       <c r="AV429" s="1"/>
-    </row>
-    <row r="430" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW429" s="1"/>
+    </row>
+    <row r="430" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A430" s="1"/>
       <c r="B430" s="1"/>
       <c r="C430" s="1"/>
@@ -22852,8 +23823,9 @@
       <c r="AT430" s="1"/>
       <c r="AU430" s="1"/>
       <c r="AV430" s="1"/>
-    </row>
-    <row r="431" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW430" s="1"/>
+    </row>
+    <row r="431" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A431" s="1"/>
       <c r="B431" s="1"/>
       <c r="C431" s="1"/>
@@ -22902,8 +23874,9 @@
       <c r="AT431" s="1"/>
       <c r="AU431" s="1"/>
       <c r="AV431" s="1"/>
-    </row>
-    <row r="432" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW431" s="1"/>
+    </row>
+    <row r="432" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A432" s="1"/>
       <c r="B432" s="1"/>
       <c r="C432" s="1"/>
@@ -22952,8 +23925,9 @@
       <c r="AT432" s="1"/>
       <c r="AU432" s="1"/>
       <c r="AV432" s="1"/>
-    </row>
-    <row r="433" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW432" s="1"/>
+    </row>
+    <row r="433" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A433" s="1"/>
       <c r="B433" s="1"/>
       <c r="C433" s="1"/>
@@ -23002,8 +23976,9 @@
       <c r="AT433" s="1"/>
       <c r="AU433" s="1"/>
       <c r="AV433" s="1"/>
-    </row>
-    <row r="434" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW433" s="1"/>
+    </row>
+    <row r="434" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A434" s="1"/>
       <c r="B434" s="1"/>
       <c r="C434" s="1"/>
@@ -23052,8 +24027,9 @@
       <c r="AT434" s="1"/>
       <c r="AU434" s="1"/>
       <c r="AV434" s="1"/>
-    </row>
-    <row r="435" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW434" s="1"/>
+    </row>
+    <row r="435" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A435" s="1"/>
       <c r="B435" s="1"/>
       <c r="C435" s="1"/>
@@ -23102,8 +24078,9 @@
       <c r="AT435" s="1"/>
       <c r="AU435" s="1"/>
       <c r="AV435" s="1"/>
-    </row>
-    <row r="436" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW435" s="1"/>
+    </row>
+    <row r="436" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A436" s="1"/>
       <c r="B436" s="1"/>
       <c r="C436" s="1"/>
@@ -23152,8 +24129,9 @@
       <c r="AT436" s="1"/>
       <c r="AU436" s="1"/>
       <c r="AV436" s="1"/>
-    </row>
-    <row r="437" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW436" s="1"/>
+    </row>
+    <row r="437" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A437" s="1"/>
       <c r="B437" s="1"/>
       <c r="C437" s="1"/>
@@ -23202,8 +24180,9 @@
       <c r="AT437" s="1"/>
       <c r="AU437" s="1"/>
       <c r="AV437" s="1"/>
-    </row>
-    <row r="438" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW437" s="1"/>
+    </row>
+    <row r="438" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A438" s="1"/>
       <c r="B438" s="1"/>
       <c r="C438" s="1"/>
@@ -23252,8 +24231,9 @@
       <c r="AT438" s="1"/>
       <c r="AU438" s="1"/>
       <c r="AV438" s="1"/>
-    </row>
-    <row r="439" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW438" s="1"/>
+    </row>
+    <row r="439" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A439" s="1"/>
       <c r="B439" s="1"/>
       <c r="C439" s="1"/>
@@ -23302,8 +24282,9 @@
       <c r="AT439" s="1"/>
       <c r="AU439" s="1"/>
       <c r="AV439" s="1"/>
-    </row>
-    <row r="440" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW439" s="1"/>
+    </row>
+    <row r="440" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A440" s="1"/>
       <c r="B440" s="1"/>
       <c r="C440" s="1"/>
@@ -23352,8 +24333,9 @@
       <c r="AT440" s="1"/>
       <c r="AU440" s="1"/>
       <c r="AV440" s="1"/>
-    </row>
-    <row r="441" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW440" s="1"/>
+    </row>
+    <row r="441" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A441" s="1"/>
       <c r="B441" s="1"/>
       <c r="C441" s="1"/>
@@ -23402,8 +24384,9 @@
       <c r="AT441" s="1"/>
       <c r="AU441" s="1"/>
       <c r="AV441" s="1"/>
-    </row>
-    <row r="442" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW441" s="1"/>
+    </row>
+    <row r="442" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A442" s="1"/>
       <c r="B442" s="1"/>
       <c r="C442" s="1"/>
@@ -23452,8 +24435,9 @@
       <c r="AT442" s="1"/>
       <c r="AU442" s="1"/>
       <c r="AV442" s="1"/>
-    </row>
-    <row r="443" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW442" s="1"/>
+    </row>
+    <row r="443" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A443" s="1"/>
       <c r="B443" s="1"/>
       <c r="C443" s="1"/>
@@ -23502,8 +24486,9 @@
       <c r="AT443" s="1"/>
       <c r="AU443" s="1"/>
       <c r="AV443" s="1"/>
-    </row>
-    <row r="444" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW443" s="1"/>
+    </row>
+    <row r="444" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A444" s="1"/>
       <c r="B444" s="1"/>
       <c r="C444" s="1"/>
@@ -23552,8 +24537,9 @@
       <c r="AT444" s="1"/>
       <c r="AU444" s="1"/>
       <c r="AV444" s="1"/>
-    </row>
-    <row r="445" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW444" s="1"/>
+    </row>
+    <row r="445" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A445" s="1"/>
       <c r="B445" s="1"/>
       <c r="C445" s="1"/>
@@ -23602,8 +24588,9 @@
       <c r="AT445" s="1"/>
       <c r="AU445" s="1"/>
       <c r="AV445" s="1"/>
-    </row>
-    <row r="446" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW445" s="1"/>
+    </row>
+    <row r="446" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A446" s="1"/>
       <c r="B446" s="1"/>
       <c r="C446" s="1"/>
@@ -23652,8 +24639,9 @@
       <c r="AT446" s="1"/>
       <c r="AU446" s="1"/>
       <c r="AV446" s="1"/>
-    </row>
-    <row r="447" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW446" s="1"/>
+    </row>
+    <row r="447" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A447" s="1"/>
       <c r="B447" s="1"/>
       <c r="C447" s="1"/>
@@ -23702,8 +24690,9 @@
       <c r="AT447" s="1"/>
       <c r="AU447" s="1"/>
       <c r="AV447" s="1"/>
-    </row>
-    <row r="448" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW447" s="1"/>
+    </row>
+    <row r="448" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A448" s="1"/>
       <c r="B448" s="1"/>
       <c r="C448" s="1"/>
@@ -23752,8 +24741,9 @@
       <c r="AT448" s="1"/>
       <c r="AU448" s="1"/>
       <c r="AV448" s="1"/>
-    </row>
-    <row r="449" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW448" s="1"/>
+    </row>
+    <row r="449" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A449" s="1"/>
       <c r="B449" s="1"/>
       <c r="C449" s="1"/>
@@ -23802,8 +24792,9 @@
       <c r="AT449" s="1"/>
       <c r="AU449" s="1"/>
       <c r="AV449" s="1"/>
-    </row>
-    <row r="450" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW449" s="1"/>
+    </row>
+    <row r="450" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A450" s="1"/>
       <c r="B450" s="1"/>
       <c r="C450" s="1"/>
@@ -23852,8 +24843,9 @@
       <c r="AT450" s="1"/>
       <c r="AU450" s="1"/>
       <c r="AV450" s="1"/>
-    </row>
-    <row r="451" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW450" s="1"/>
+    </row>
+    <row r="451" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A451" s="1"/>
       <c r="B451" s="1"/>
       <c r="C451" s="1"/>
@@ -23902,8 +24894,9 @@
       <c r="AT451" s="1"/>
       <c r="AU451" s="1"/>
       <c r="AV451" s="1"/>
-    </row>
-    <row r="452" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW451" s="1"/>
+    </row>
+    <row r="452" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A452" s="1"/>
       <c r="B452" s="1"/>
       <c r="C452" s="1"/>
@@ -23952,8 +24945,9 @@
       <c r="AT452" s="1"/>
       <c r="AU452" s="1"/>
       <c r="AV452" s="1"/>
-    </row>
-    <row r="453" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW452" s="1"/>
+    </row>
+    <row r="453" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A453" s="1"/>
       <c r="B453" s="1"/>
       <c r="C453" s="1"/>
@@ -24002,8 +24996,9 @@
       <c r="AT453" s="1"/>
       <c r="AU453" s="1"/>
       <c r="AV453" s="1"/>
-    </row>
-    <row r="454" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW453" s="1"/>
+    </row>
+    <row r="454" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A454" s="1"/>
       <c r="B454" s="1"/>
       <c r="C454" s="1"/>
@@ -24052,8 +25047,9 @@
       <c r="AT454" s="1"/>
       <c r="AU454" s="1"/>
       <c r="AV454" s="1"/>
-    </row>
-    <row r="455" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW454" s="1"/>
+    </row>
+    <row r="455" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A455" s="1"/>
       <c r="B455" s="1"/>
       <c r="C455" s="1"/>
@@ -24102,8 +25098,9 @@
       <c r="AT455" s="1"/>
       <c r="AU455" s="1"/>
       <c r="AV455" s="1"/>
-    </row>
-    <row r="456" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW455" s="1"/>
+    </row>
+    <row r="456" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A456" s="1"/>
       <c r="B456" s="1"/>
       <c r="C456" s="1"/>
@@ -24152,8 +25149,9 @@
       <c r="AT456" s="1"/>
       <c r="AU456" s="1"/>
       <c r="AV456" s="1"/>
-    </row>
-    <row r="457" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW456" s="1"/>
+    </row>
+    <row r="457" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A457" s="1"/>
       <c r="B457" s="1"/>
       <c r="C457" s="1"/>
@@ -24202,8 +25200,9 @@
       <c r="AT457" s="1"/>
       <c r="AU457" s="1"/>
       <c r="AV457" s="1"/>
-    </row>
-    <row r="458" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW457" s="1"/>
+    </row>
+    <row r="458" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A458" s="1"/>
       <c r="B458" s="1"/>
       <c r="C458" s="1"/>
@@ -24252,8 +25251,9 @@
       <c r="AT458" s="1"/>
       <c r="AU458" s="1"/>
       <c r="AV458" s="1"/>
-    </row>
-    <row r="459" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW458" s="1"/>
+    </row>
+    <row r="459" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A459" s="1"/>
       <c r="B459" s="1"/>
       <c r="C459" s="1"/>
@@ -24302,8 +25302,9 @@
       <c r="AT459" s="1"/>
       <c r="AU459" s="1"/>
       <c r="AV459" s="1"/>
-    </row>
-    <row r="460" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW459" s="1"/>
+    </row>
+    <row r="460" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A460" s="1"/>
       <c r="B460" s="1"/>
       <c r="C460" s="1"/>
@@ -24352,8 +25353,9 @@
       <c r="AT460" s="1"/>
       <c r="AU460" s="1"/>
       <c r="AV460" s="1"/>
-    </row>
-    <row r="461" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW460" s="1"/>
+    </row>
+    <row r="461" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A461" s="1"/>
       <c r="B461" s="1"/>
       <c r="C461" s="1"/>
@@ -24402,8 +25404,9 @@
       <c r="AT461" s="1"/>
       <c r="AU461" s="1"/>
       <c r="AV461" s="1"/>
-    </row>
-    <row r="462" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW461" s="1"/>
+    </row>
+    <row r="462" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A462" s="1"/>
       <c r="B462" s="1"/>
       <c r="C462" s="1"/>
@@ -24452,8 +25455,9 @@
       <c r="AT462" s="1"/>
       <c r="AU462" s="1"/>
       <c r="AV462" s="1"/>
-    </row>
-    <row r="463" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW462" s="1"/>
+    </row>
+    <row r="463" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A463" s="1"/>
       <c r="B463" s="1"/>
       <c r="C463" s="1"/>
@@ -24502,8 +25506,9 @@
       <c r="AT463" s="1"/>
       <c r="AU463" s="1"/>
       <c r="AV463" s="1"/>
-    </row>
-    <row r="464" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW463" s="1"/>
+    </row>
+    <row r="464" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A464" s="1"/>
       <c r="B464" s="1"/>
       <c r="C464" s="1"/>
@@ -24552,8 +25557,9 @@
       <c r="AT464" s="1"/>
       <c r="AU464" s="1"/>
       <c r="AV464" s="1"/>
-    </row>
-    <row r="465" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW464" s="1"/>
+    </row>
+    <row r="465" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A465" s="1"/>
       <c r="B465" s="1"/>
       <c r="C465" s="1"/>
@@ -24602,8 +25608,9 @@
       <c r="AT465" s="1"/>
       <c r="AU465" s="1"/>
       <c r="AV465" s="1"/>
-    </row>
-    <row r="466" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW465" s="1"/>
+    </row>
+    <row r="466" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A466" s="1"/>
       <c r="B466" s="1"/>
       <c r="C466" s="1"/>
@@ -24652,8 +25659,9 @@
       <c r="AT466" s="1"/>
       <c r="AU466" s="1"/>
       <c r="AV466" s="1"/>
-    </row>
-    <row r="467" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW466" s="1"/>
+    </row>
+    <row r="467" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A467" s="1"/>
       <c r="B467" s="1"/>
       <c r="C467" s="1"/>
@@ -24702,8 +25710,9 @@
       <c r="AT467" s="1"/>
       <c r="AU467" s="1"/>
       <c r="AV467" s="1"/>
-    </row>
-    <row r="468" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW467" s="1"/>
+    </row>
+    <row r="468" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A468" s="1"/>
       <c r="B468" s="1"/>
       <c r="C468" s="1"/>
@@ -24752,8 +25761,9 @@
       <c r="AT468" s="1"/>
       <c r="AU468" s="1"/>
       <c r="AV468" s="1"/>
-    </row>
-    <row r="469" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW468" s="1"/>
+    </row>
+    <row r="469" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A469" s="1"/>
       <c r="B469" s="1"/>
       <c r="C469" s="1"/>
@@ -24802,8 +25812,9 @@
       <c r="AT469" s="1"/>
       <c r="AU469" s="1"/>
       <c r="AV469" s="1"/>
-    </row>
-    <row r="470" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW469" s="1"/>
+    </row>
+    <row r="470" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A470" s="1"/>
       <c r="B470" s="1"/>
       <c r="C470" s="1"/>
@@ -24852,8 +25863,9 @@
       <c r="AT470" s="1"/>
       <c r="AU470" s="1"/>
       <c r="AV470" s="1"/>
-    </row>
-    <row r="471" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW470" s="1"/>
+    </row>
+    <row r="471" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A471" s="1"/>
       <c r="B471" s="1"/>
       <c r="C471" s="1"/>
@@ -24902,8 +25914,9 @@
       <c r="AT471" s="1"/>
       <c r="AU471" s="1"/>
       <c r="AV471" s="1"/>
-    </row>
-    <row r="472" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW471" s="1"/>
+    </row>
+    <row r="472" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A472" s="1"/>
       <c r="B472" s="1"/>
       <c r="C472" s="1"/>
@@ -24952,8 +25965,9 @@
       <c r="AT472" s="1"/>
       <c r="AU472" s="1"/>
       <c r="AV472" s="1"/>
-    </row>
-    <row r="473" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW472" s="1"/>
+    </row>
+    <row r="473" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A473" s="1"/>
       <c r="B473" s="1"/>
       <c r="C473" s="1"/>
@@ -25002,8 +26016,9 @@
       <c r="AT473" s="1"/>
       <c r="AU473" s="1"/>
       <c r="AV473" s="1"/>
-    </row>
-    <row r="474" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW473" s="1"/>
+    </row>
+    <row r="474" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A474" s="1"/>
       <c r="B474" s="1"/>
       <c r="C474" s="1"/>
@@ -25052,8 +26067,9 @@
       <c r="AT474" s="1"/>
       <c r="AU474" s="1"/>
       <c r="AV474" s="1"/>
-    </row>
-    <row r="475" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW474" s="1"/>
+    </row>
+    <row r="475" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A475" s="1"/>
       <c r="B475" s="1"/>
       <c r="C475" s="1"/>
@@ -25102,8 +26118,9 @@
       <c r="AT475" s="1"/>
       <c r="AU475" s="1"/>
       <c r="AV475" s="1"/>
-    </row>
-    <row r="476" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW475" s="1"/>
+    </row>
+    <row r="476" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A476" s="1"/>
       <c r="B476" s="1"/>
       <c r="C476" s="1"/>
@@ -25152,8 +26169,9 @@
       <c r="AT476" s="1"/>
       <c r="AU476" s="1"/>
       <c r="AV476" s="1"/>
-    </row>
-    <row r="477" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW476" s="1"/>
+    </row>
+    <row r="477" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A477" s="1"/>
       <c r="B477" s="1"/>
       <c r="C477" s="1"/>
@@ -25202,8 +26220,9 @@
       <c r="AT477" s="1"/>
       <c r="AU477" s="1"/>
       <c r="AV477" s="1"/>
-    </row>
-    <row r="478" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW477" s="1"/>
+    </row>
+    <row r="478" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A478" s="1"/>
       <c r="B478" s="1"/>
       <c r="C478" s="1"/>
@@ -25252,8 +26271,9 @@
       <c r="AT478" s="1"/>
       <c r="AU478" s="1"/>
       <c r="AV478" s="1"/>
-    </row>
-    <row r="479" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW478" s="1"/>
+    </row>
+    <row r="479" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A479" s="1"/>
       <c r="B479" s="1"/>
       <c r="C479" s="1"/>
@@ -25302,8 +26322,9 @@
       <c r="AT479" s="1"/>
       <c r="AU479" s="1"/>
       <c r="AV479" s="1"/>
-    </row>
-    <row r="480" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW479" s="1"/>
+    </row>
+    <row r="480" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A480" s="1"/>
       <c r="B480" s="1"/>
       <c r="C480" s="1"/>
@@ -25352,8 +26373,9 @@
       <c r="AT480" s="1"/>
       <c r="AU480" s="1"/>
       <c r="AV480" s="1"/>
-    </row>
-    <row r="481" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW480" s="1"/>
+    </row>
+    <row r="481" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A481" s="1"/>
       <c r="B481" s="1"/>
       <c r="C481" s="1"/>
@@ -25402,8 +26424,9 @@
       <c r="AT481" s="1"/>
       <c r="AU481" s="1"/>
       <c r="AV481" s="1"/>
-    </row>
-    <row r="482" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW481" s="1"/>
+    </row>
+    <row r="482" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A482" s="1"/>
       <c r="B482" s="1"/>
       <c r="C482" s="1"/>
@@ -25452,8 +26475,9 @@
       <c r="AT482" s="1"/>
       <c r="AU482" s="1"/>
       <c r="AV482" s="1"/>
-    </row>
-    <row r="483" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW482" s="1"/>
+    </row>
+    <row r="483" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A483" s="1"/>
       <c r="B483" s="1"/>
       <c r="C483" s="1"/>
@@ -25502,8 +26526,9 @@
       <c r="AT483" s="1"/>
       <c r="AU483" s="1"/>
       <c r="AV483" s="1"/>
-    </row>
-    <row r="484" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW483" s="1"/>
+    </row>
+    <row r="484" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A484" s="1"/>
       <c r="B484" s="1"/>
       <c r="C484" s="1"/>
@@ -25552,8 +26577,9 @@
       <c r="AT484" s="1"/>
       <c r="AU484" s="1"/>
       <c r="AV484" s="1"/>
-    </row>
-    <row r="485" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW484" s="1"/>
+    </row>
+    <row r="485" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A485" s="1"/>
       <c r="B485" s="1"/>
       <c r="C485" s="1"/>
@@ -25602,8 +26628,9 @@
       <c r="AT485" s="1"/>
       <c r="AU485" s="1"/>
       <c r="AV485" s="1"/>
-    </row>
-    <row r="486" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW485" s="1"/>
+    </row>
+    <row r="486" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A486" s="1"/>
       <c r="B486" s="1"/>
       <c r="C486" s="1"/>
@@ -25652,8 +26679,9 @@
       <c r="AT486" s="1"/>
       <c r="AU486" s="1"/>
       <c r="AV486" s="1"/>
-    </row>
-    <row r="487" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW486" s="1"/>
+    </row>
+    <row r="487" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A487" s="1"/>
       <c r="B487" s="1"/>
       <c r="C487" s="1"/>
@@ -25702,8 +26730,9 @@
       <c r="AT487" s="1"/>
       <c r="AU487" s="1"/>
       <c r="AV487" s="1"/>
-    </row>
-    <row r="488" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW487" s="1"/>
+    </row>
+    <row r="488" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A488" s="1"/>
       <c r="B488" s="1"/>
       <c r="C488" s="1"/>
@@ -25752,8 +26781,9 @@
       <c r="AT488" s="1"/>
       <c r="AU488" s="1"/>
       <c r="AV488" s="1"/>
-    </row>
-    <row r="489" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW488" s="1"/>
+    </row>
+    <row r="489" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A489" s="1"/>
       <c r="B489" s="1"/>
       <c r="C489" s="1"/>
@@ -25802,8 +26832,9 @@
       <c r="AT489" s="1"/>
       <c r="AU489" s="1"/>
       <c r="AV489" s="1"/>
-    </row>
-    <row r="490" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW489" s="1"/>
+    </row>
+    <row r="490" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A490" s="1"/>
       <c r="B490" s="1"/>
       <c r="C490" s="1"/>
@@ -25852,8 +26883,9 @@
       <c r="AT490" s="1"/>
       <c r="AU490" s="1"/>
       <c r="AV490" s="1"/>
-    </row>
-    <row r="491" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW490" s="1"/>
+    </row>
+    <row r="491" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A491" s="1"/>
       <c r="B491" s="1"/>
       <c r="C491" s="1"/>
@@ -25902,8 +26934,9 @@
       <c r="AT491" s="1"/>
       <c r="AU491" s="1"/>
       <c r="AV491" s="1"/>
-    </row>
-    <row r="492" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW491" s="1"/>
+    </row>
+    <row r="492" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A492" s="1"/>
       <c r="B492" s="1"/>
       <c r="C492" s="1"/>
@@ -25952,8 +26985,9 @@
       <c r="AT492" s="1"/>
       <c r="AU492" s="1"/>
       <c r="AV492" s="1"/>
-    </row>
-    <row r="493" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW492" s="1"/>
+    </row>
+    <row r="493" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A493" s="1"/>
       <c r="B493" s="1"/>
       <c r="C493" s="1"/>
@@ -26002,8 +27036,9 @@
       <c r="AT493" s="1"/>
       <c r="AU493" s="1"/>
       <c r="AV493" s="1"/>
-    </row>
-    <row r="494" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW493" s="1"/>
+    </row>
+    <row r="494" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A494" s="1"/>
       <c r="B494" s="1"/>
       <c r="C494" s="1"/>
@@ -26052,8 +27087,9 @@
       <c r="AT494" s="1"/>
       <c r="AU494" s="1"/>
       <c r="AV494" s="1"/>
-    </row>
-    <row r="495" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW494" s="1"/>
+    </row>
+    <row r="495" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A495" s="1"/>
       <c r="B495" s="1"/>
       <c r="C495" s="1"/>
@@ -26102,8 +27138,9 @@
       <c r="AT495" s="1"/>
       <c r="AU495" s="1"/>
       <c r="AV495" s="1"/>
-    </row>
-    <row r="496" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW495" s="1"/>
+    </row>
+    <row r="496" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A496" s="1"/>
       <c r="B496" s="1"/>
       <c r="C496" s="1"/>
@@ -26152,8 +27189,9 @@
       <c r="AT496" s="1"/>
       <c r="AU496" s="1"/>
       <c r="AV496" s="1"/>
-    </row>
-    <row r="497" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW496" s="1"/>
+    </row>
+    <row r="497" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A497" s="1"/>
       <c r="B497" s="1"/>
       <c r="C497" s="1"/>
@@ -26202,8 +27240,9 @@
       <c r="AT497" s="1"/>
       <c r="AU497" s="1"/>
       <c r="AV497" s="1"/>
-    </row>
-    <row r="498" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW497" s="1"/>
+    </row>
+    <row r="498" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A498" s="1"/>
       <c r="B498" s="1"/>
       <c r="C498" s="1"/>
@@ -26252,8 +27291,9 @@
       <c r="AT498" s="1"/>
       <c r="AU498" s="1"/>
       <c r="AV498" s="1"/>
-    </row>
-    <row r="499" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW498" s="1"/>
+    </row>
+    <row r="499" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A499" s="1"/>
       <c r="B499" s="1"/>
       <c r="C499" s="1"/>
@@ -26302,8 +27342,9 @@
       <c r="AT499" s="1"/>
       <c r="AU499" s="1"/>
       <c r="AV499" s="1"/>
-    </row>
-    <row r="500" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW499" s="1"/>
+    </row>
+    <row r="500" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A500" s="1"/>
       <c r="B500" s="1"/>
       <c r="C500" s="1"/>
@@ -26352,6 +27393,7 @@
       <c r="AT500" s="1"/>
       <c r="AU500" s="1"/>
       <c r="AV500" s="1"/>
+      <c r="AW500" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
